--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/09-report/CYC-2-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/09-report/CYC-2-cycle-report.xlsx
@@ -161,7 +161,7 @@
     <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef)</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T03:53:53.009Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T04:13:34.027Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -3358,7 +3358,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T03:53:53.694Z</t>
+    <t>2026-10-02T04:13:34.804Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -13586,7 +13586,7 @@
         <v>1026</v>
       </c>
       <c r="E2" s="2">
-        <v>530</v>
+        <v>490</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -13704,7 +13704,7 @@
         <v>1026</v>
       </c>
       <c r="E8" s="2">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -13722,7 +13722,7 @@
         <v>1026</v>
       </c>
       <c r="E9" s="2">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -13740,7 +13740,7 @@
         <v>1026</v>
       </c>
       <c r="E10" s="2">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -13758,7 +13758,7 @@
         <v>1026</v>
       </c>
       <c r="E11" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -13776,7 +13776,7 @@
         <v>1026</v>
       </c>
       <c r="E12" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -13794,7 +13794,7 @@
         <v>1026</v>
       </c>
       <c r="E13" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -13872,7 +13872,7 @@
         <v>1026</v>
       </c>
       <c r="E17" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -13890,7 +13890,7 @@
         <v>1026</v>
       </c>
       <c r="E18" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -13968,7 +13968,7 @@
         <v>1026</v>
       </c>
       <c r="E22" s="2">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F22" s="2"/>
     </row>
@@ -14006,7 +14006,7 @@
         <v>1026</v>
       </c>
       <c r="E24" s="2">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -14024,7 +14024,7 @@
         <v>1026</v>
       </c>
       <c r="E25" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -14042,7 +14042,7 @@
         <v>1026</v>
       </c>
       <c r="E26" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -14060,7 +14060,7 @@
         <v>1026</v>
       </c>
       <c r="E27" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -14078,7 +14078,7 @@
         <v>1026</v>
       </c>
       <c r="E28" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -14096,7 +14096,7 @@
         <v>1026</v>
       </c>
       <c r="E29" s="2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -14132,7 +14132,7 @@
         <v>1026</v>
       </c>
       <c r="E31" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -14150,7 +14150,7 @@
         <v>1026</v>
       </c>
       <c r="E32" s="2">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F32" s="2"/>
     </row>
@@ -14188,7 +14188,7 @@
         <v>1026</v>
       </c>
       <c r="E34" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -14264,7 +14264,7 @@
         <v>1026</v>
       </c>
       <c r="E38" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F38" s="2"/>
     </row>
@@ -14302,7 +14302,7 @@
         <v>1026</v>
       </c>
       <c r="E40" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -14320,7 +14320,7 @@
         <v>1026</v>
       </c>
       <c r="E41" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F41" s="2"/>
     </row>
@@ -14418,7 +14418,7 @@
         <v>1026</v>
       </c>
       <c r="E46" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -14454,7 +14454,7 @@
         <v>1026</v>
       </c>
       <c r="E48" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F48" s="2"/>
     </row>
@@ -14492,7 +14492,7 @@
         <v>1026</v>
       </c>
       <c r="E50" s="2">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -14510,7 +14510,7 @@
         <v>1026</v>
       </c>
       <c r="E51" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -14528,7 +14528,7 @@
         <v>1026</v>
       </c>
       <c r="E52" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F52" s="2"/>
     </row>
@@ -14646,7 +14646,7 @@
         <v>1026</v>
       </c>
       <c r="E58" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -14664,7 +14664,7 @@
         <v>1026</v>
       </c>
       <c r="E59" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F59" s="2"/>
     </row>
@@ -14702,7 +14702,7 @@
         <v>1026</v>
       </c>
       <c r="E61" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F61" s="2"/>
     </row>
@@ -14800,7 +14800,7 @@
         <v>1026</v>
       </c>
       <c r="E66" s="2">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -14818,7 +14818,7 @@
         <v>1026</v>
       </c>
       <c r="E67" s="2">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -14836,7 +14836,7 @@
         <v>1026</v>
       </c>
       <c r="E68" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F68" s="2"/>
     </row>
@@ -14894,7 +14894,7 @@
         <v>1026</v>
       </c>
       <c r="E71" s="2">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -14930,7 +14930,7 @@
         <v>1026</v>
       </c>
       <c r="E73" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F73" s="2"/>
     </row>
@@ -14968,7 +14968,7 @@
         <v>1026</v>
       </c>
       <c r="E75" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -14986,7 +14986,7 @@
         <v>1026</v>
       </c>
       <c r="E76" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -15004,7 +15004,7 @@
         <v>1026</v>
       </c>
       <c r="E77" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -15022,7 +15022,7 @@
         <v>1026</v>
       </c>
       <c r="E78" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F78" s="2"/>
     </row>
@@ -15080,7 +15080,7 @@
         <v>1026</v>
       </c>
       <c r="E81" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -15098,7 +15098,7 @@
         <v>1026</v>
       </c>
       <c r="E82" s="2">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -15116,7 +15116,7 @@
         <v>1026</v>
       </c>
       <c r="E83" s="2">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F83" s="2"/>
     </row>
@@ -15194,7 +15194,7 @@
         <v>1026</v>
       </c>
       <c r="E87" s="2">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -15212,7 +15212,7 @@
         <v>1026</v>
       </c>
       <c r="E88" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -15230,7 +15230,7 @@
         <v>1026</v>
       </c>
       <c r="E89" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -15248,7 +15248,7 @@
         <v>1026</v>
       </c>
       <c r="E90" s="2">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -15266,7 +15266,7 @@
         <v>1026</v>
       </c>
       <c r="E91" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F91" s="2"/>
     </row>
@@ -15324,7 +15324,7 @@
         <v>1026</v>
       </c>
       <c r="E94" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -15362,7 +15362,7 @@
         <v>1026</v>
       </c>
       <c r="E96" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F96" s="2"/>
     </row>
@@ -15440,7 +15440,7 @@
         <v>1026</v>
       </c>
       <c r="E100" s="2">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="F100" s="2"/>
     </row>
@@ -15558,7 +15558,7 @@
         <v>1026</v>
       </c>
       <c r="E106" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -15596,7 +15596,7 @@
         <v>1026</v>
       </c>
       <c r="E108" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F108" s="2"/>
     </row>
@@ -15774,7 +15774,7 @@
         <v>1026</v>
       </c>
       <c r="E117" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -15872,7 +15872,7 @@
         <v>1026</v>
       </c>
       <c r="E122" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -15890,7 +15890,7 @@
         <v>1026</v>
       </c>
       <c r="E123" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -15908,7 +15908,7 @@
         <v>1026</v>
       </c>
       <c r="E124" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -15926,7 +15926,7 @@
         <v>1026</v>
       </c>
       <c r="E125" s="2">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -15944,7 +15944,7 @@
         <v>1026</v>
       </c>
       <c r="E126" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -15962,7 +15962,7 @@
         <v>1026</v>
       </c>
       <c r="E127" s="2">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -15980,7 +15980,7 @@
         <v>1026</v>
       </c>
       <c r="E128" s="2">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -15998,7 +15998,7 @@
         <v>1026</v>
       </c>
       <c r="E129" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -16034,7 +16034,7 @@
         <v>1026</v>
       </c>
       <c r="E131" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -16070,7 +16070,7 @@
         <v>1026</v>
       </c>
       <c r="E133" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F133" s="2"/>
     </row>
@@ -16106,7 +16106,7 @@
         <v>1026</v>
       </c>
       <c r="E135" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F135" s="2"/>
     </row>
@@ -16124,7 +16124,7 @@
         <v>1026</v>
       </c>
       <c r="E136" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F136" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/09-report/CYC-2-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/09-report/CYC-2-cycle-report.xlsx
@@ -161,7 +161,7 @@
     <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef)</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T04:13:34.027Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T15:08:14.059Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -3358,7 +3358,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T04:13:34.804Z</t>
+    <t>2026-10-02T15:08:14.878Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -13586,7 +13586,7 @@
         <v>1026</v>
       </c>
       <c r="E2" s="2">
-        <v>490</v>
+        <v>538</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -13704,7 +13704,7 @@
         <v>1026</v>
       </c>
       <c r="E8" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -13722,7 +13722,7 @@
         <v>1026</v>
       </c>
       <c r="E9" s="2">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -13740,7 +13740,7 @@
         <v>1026</v>
       </c>
       <c r="E10" s="2">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -13758,7 +13758,7 @@
         <v>1026</v>
       </c>
       <c r="E11" s="2">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -13776,7 +13776,7 @@
         <v>1026</v>
       </c>
       <c r="E12" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -13794,7 +13794,7 @@
         <v>1026</v>
       </c>
       <c r="E13" s="2">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -13872,7 +13872,7 @@
         <v>1026</v>
       </c>
       <c r="E17" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -13890,7 +13890,7 @@
         <v>1026</v>
       </c>
       <c r="E18" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -13968,7 +13968,7 @@
         <v>1026</v>
       </c>
       <c r="E22" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F22" s="2"/>
     </row>
@@ -14006,7 +14006,7 @@
         <v>1026</v>
       </c>
       <c r="E24" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -14024,7 +14024,7 @@
         <v>1026</v>
       </c>
       <c r="E25" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -14042,7 +14042,7 @@
         <v>1026</v>
       </c>
       <c r="E26" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -14078,7 +14078,7 @@
         <v>1026</v>
       </c>
       <c r="E28" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -14096,7 +14096,7 @@
         <v>1026</v>
       </c>
       <c r="E29" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -14114,7 +14114,7 @@
         <v>1026</v>
       </c>
       <c r="E30" s="2">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -14150,7 +14150,7 @@
         <v>1026</v>
       </c>
       <c r="E32" s="2">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F32" s="2"/>
     </row>
@@ -14188,7 +14188,7 @@
         <v>1026</v>
       </c>
       <c r="E34" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -14206,7 +14206,7 @@
         <v>1026</v>
       </c>
       <c r="E35" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F35" s="2"/>
     </row>
@@ -14264,7 +14264,7 @@
         <v>1026</v>
       </c>
       <c r="E38" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F38" s="2"/>
     </row>
@@ -14302,7 +14302,7 @@
         <v>1026</v>
       </c>
       <c r="E40" s="2">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -14320,7 +14320,7 @@
         <v>1026</v>
       </c>
       <c r="E41" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F41" s="2"/>
     </row>
@@ -14418,7 +14418,7 @@
         <v>1026</v>
       </c>
       <c r="E46" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -14436,7 +14436,7 @@
         <v>1026</v>
       </c>
       <c r="E47" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -14454,7 +14454,7 @@
         <v>1026</v>
       </c>
       <c r="E48" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F48" s="2"/>
     </row>
@@ -14492,7 +14492,7 @@
         <v>1026</v>
       </c>
       <c r="E50" s="2">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -14510,7 +14510,7 @@
         <v>1026</v>
       </c>
       <c r="E51" s="2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -14528,7 +14528,7 @@
         <v>1026</v>
       </c>
       <c r="E52" s="2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F52" s="2"/>
     </row>
@@ -14646,7 +14646,7 @@
         <v>1026</v>
       </c>
       <c r="E58" s="2">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -14664,7 +14664,7 @@
         <v>1026</v>
       </c>
       <c r="E59" s="2">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F59" s="2"/>
     </row>
@@ -14702,7 +14702,7 @@
         <v>1026</v>
       </c>
       <c r="E61" s="2">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F61" s="2"/>
     </row>
@@ -14800,7 +14800,7 @@
         <v>1026</v>
       </c>
       <c r="E66" s="2">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -14818,7 +14818,7 @@
         <v>1026</v>
       </c>
       <c r="E67" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -14836,7 +14836,7 @@
         <v>1026</v>
       </c>
       <c r="E68" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F68" s="2"/>
     </row>
@@ -14894,7 +14894,7 @@
         <v>1026</v>
       </c>
       <c r="E71" s="2">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -14912,7 +14912,7 @@
         <v>1026</v>
       </c>
       <c r="E72" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -14930,7 +14930,7 @@
         <v>1026</v>
       </c>
       <c r="E73" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F73" s="2"/>
     </row>
@@ -14968,7 +14968,7 @@
         <v>1026</v>
       </c>
       <c r="E75" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -14986,7 +14986,7 @@
         <v>1026</v>
       </c>
       <c r="E76" s="2">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -15004,7 +15004,7 @@
         <v>1026</v>
       </c>
       <c r="E77" s="2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -15022,7 +15022,7 @@
         <v>1026</v>
       </c>
       <c r="E78" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F78" s="2"/>
     </row>
@@ -15080,7 +15080,7 @@
         <v>1026</v>
       </c>
       <c r="E81" s="2">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -15098,7 +15098,7 @@
         <v>1026</v>
       </c>
       <c r="E82" s="2">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -15116,7 +15116,7 @@
         <v>1026</v>
       </c>
       <c r="E83" s="2">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F83" s="2"/>
     </row>
@@ -15194,7 +15194,7 @@
         <v>1026</v>
       </c>
       <c r="E87" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -15212,7 +15212,7 @@
         <v>1026</v>
       </c>
       <c r="E88" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -15230,7 +15230,7 @@
         <v>1026</v>
       </c>
       <c r="E89" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -15248,7 +15248,7 @@
         <v>1026</v>
       </c>
       <c r="E90" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -15266,7 +15266,7 @@
         <v>1026</v>
       </c>
       <c r="E91" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F91" s="2"/>
     </row>
@@ -15324,7 +15324,7 @@
         <v>1026</v>
       </c>
       <c r="E94" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -15362,7 +15362,7 @@
         <v>1026</v>
       </c>
       <c r="E96" s="2">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="F96" s="2"/>
     </row>
@@ -15440,7 +15440,7 @@
         <v>1026</v>
       </c>
       <c r="E100" s="2">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F100" s="2"/>
     </row>
@@ -15558,7 +15558,7 @@
         <v>1026</v>
       </c>
       <c r="E106" s="2">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -15596,7 +15596,7 @@
         <v>1026</v>
       </c>
       <c r="E108" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F108" s="2"/>
     </row>
@@ -15774,7 +15774,7 @@
         <v>1026</v>
       </c>
       <c r="E117" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -15890,7 +15890,7 @@
         <v>1026</v>
       </c>
       <c r="E123" s="2">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -15926,7 +15926,7 @@
         <v>1026</v>
       </c>
       <c r="E125" s="2">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -15944,7 +15944,7 @@
         <v>1026</v>
       </c>
       <c r="E126" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -15962,7 +15962,7 @@
         <v>1026</v>
       </c>
       <c r="E127" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -15980,7 +15980,7 @@
         <v>1026</v>
       </c>
       <c r="E128" s="2">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -15998,7 +15998,7 @@
         <v>1026</v>
       </c>
       <c r="E129" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -16016,7 +16016,7 @@
         <v>1026</v>
       </c>
       <c r="E130" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -16034,7 +16034,7 @@
         <v>1026</v>
       </c>
       <c r="E131" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -16052,7 +16052,7 @@
         <v>1026</v>
       </c>
       <c r="E132" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -16070,7 +16070,7 @@
         <v>1026</v>
       </c>
       <c r="E133" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F133" s="2"/>
     </row>
@@ -16124,7 +16124,7 @@
         <v>1026</v>
       </c>
       <c r="E136" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F136" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/09-report/CYC-2-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/09-report/CYC-2-cycle-report.xlsx
@@ -161,7 +161,7 @@
     <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef)</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T15:08:14.059Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T15:29:29.806Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -3358,7 +3358,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T15:08:14.878Z</t>
+    <t>2026-10-02T15:29:30.854Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -13586,7 +13586,7 @@
         <v>1026</v>
       </c>
       <c r="E2" s="2">
-        <v>538</v>
+        <v>594</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -13704,7 +13704,7 @@
         <v>1026</v>
       </c>
       <c r="E8" s="2">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -13722,7 +13722,7 @@
         <v>1026</v>
       </c>
       <c r="E9" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -13740,7 +13740,7 @@
         <v>1026</v>
       </c>
       <c r="E10" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -13758,7 +13758,7 @@
         <v>1026</v>
       </c>
       <c r="E11" s="2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -13776,7 +13776,7 @@
         <v>1026</v>
       </c>
       <c r="E12" s="2">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -13794,7 +13794,7 @@
         <v>1026</v>
       </c>
       <c r="E13" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -13872,7 +13872,7 @@
         <v>1026</v>
       </c>
       <c r="E17" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -13890,7 +13890,7 @@
         <v>1026</v>
       </c>
       <c r="E18" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -13968,7 +13968,7 @@
         <v>1026</v>
       </c>
       <c r="E22" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F22" s="2"/>
     </row>
@@ -14006,7 +14006,7 @@
         <v>1026</v>
       </c>
       <c r="E24" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -14024,7 +14024,7 @@
         <v>1026</v>
       </c>
       <c r="E25" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -14042,7 +14042,7 @@
         <v>1026</v>
       </c>
       <c r="E26" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -14060,7 +14060,7 @@
         <v>1026</v>
       </c>
       <c r="E27" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -14078,7 +14078,7 @@
         <v>1026</v>
       </c>
       <c r="E28" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -14096,7 +14096,7 @@
         <v>1026</v>
       </c>
       <c r="E29" s="2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -14114,7 +14114,7 @@
         <v>1026</v>
       </c>
       <c r="E30" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -14132,7 +14132,7 @@
         <v>1026</v>
       </c>
       <c r="E31" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -14150,7 +14150,7 @@
         <v>1026</v>
       </c>
       <c r="E32" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F32" s="2"/>
     </row>
@@ -14188,7 +14188,7 @@
         <v>1026</v>
       </c>
       <c r="E34" s="2">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -14206,7 +14206,7 @@
         <v>1026</v>
       </c>
       <c r="E35" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F35" s="2"/>
     </row>
@@ -14264,7 +14264,7 @@
         <v>1026</v>
       </c>
       <c r="E38" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F38" s="2"/>
     </row>
@@ -14302,7 +14302,7 @@
         <v>1026</v>
       </c>
       <c r="E40" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -14320,7 +14320,7 @@
         <v>1026</v>
       </c>
       <c r="E41" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F41" s="2"/>
     </row>
@@ -14418,7 +14418,7 @@
         <v>1026</v>
       </c>
       <c r="E46" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -14436,7 +14436,7 @@
         <v>1026</v>
       </c>
       <c r="E47" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -14454,7 +14454,7 @@
         <v>1026</v>
       </c>
       <c r="E48" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F48" s="2"/>
     </row>
@@ -14492,7 +14492,7 @@
         <v>1026</v>
       </c>
       <c r="E50" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -14510,7 +14510,7 @@
         <v>1026</v>
       </c>
       <c r="E51" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -14528,7 +14528,7 @@
         <v>1026</v>
       </c>
       <c r="E52" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F52" s="2"/>
     </row>
@@ -14646,7 +14646,7 @@
         <v>1026</v>
       </c>
       <c r="E58" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -14664,7 +14664,7 @@
         <v>1026</v>
       </c>
       <c r="E59" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F59" s="2"/>
     </row>
@@ -14702,7 +14702,7 @@
         <v>1026</v>
       </c>
       <c r="E61" s="2">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F61" s="2"/>
     </row>
@@ -14800,7 +14800,7 @@
         <v>1026</v>
       </c>
       <c r="E66" s="2">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -14818,7 +14818,7 @@
         <v>1026</v>
       </c>
       <c r="E67" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -14836,7 +14836,7 @@
         <v>1026</v>
       </c>
       <c r="E68" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F68" s="2"/>
     </row>
@@ -14894,7 +14894,7 @@
         <v>1026</v>
       </c>
       <c r="E71" s="2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -14912,7 +14912,7 @@
         <v>1026</v>
       </c>
       <c r="E72" s="2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -14968,7 +14968,7 @@
         <v>1026</v>
       </c>
       <c r="E75" s="2">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -14986,7 +14986,7 @@
         <v>1026</v>
       </c>
       <c r="E76" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -15004,7 +15004,7 @@
         <v>1026</v>
       </c>
       <c r="E77" s="2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -15022,7 +15022,7 @@
         <v>1026</v>
       </c>
       <c r="E78" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F78" s="2"/>
     </row>
@@ -15080,7 +15080,7 @@
         <v>1026</v>
       </c>
       <c r="E81" s="2">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -15098,7 +15098,7 @@
         <v>1026</v>
       </c>
       <c r="E82" s="2">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -15116,7 +15116,7 @@
         <v>1026</v>
       </c>
       <c r="E83" s="2">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F83" s="2"/>
     </row>
@@ -15194,7 +15194,7 @@
         <v>1026</v>
       </c>
       <c r="E87" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -15212,7 +15212,7 @@
         <v>1026</v>
       </c>
       <c r="E88" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -15230,7 +15230,7 @@
         <v>1026</v>
       </c>
       <c r="E89" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -15248,7 +15248,7 @@
         <v>1026</v>
       </c>
       <c r="E90" s="2">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -15266,7 +15266,7 @@
         <v>1026</v>
       </c>
       <c r="E91" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F91" s="2"/>
     </row>
@@ -15324,7 +15324,7 @@
         <v>1026</v>
       </c>
       <c r="E94" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -15362,7 +15362,7 @@
         <v>1026</v>
       </c>
       <c r="E96" s="2">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="F96" s="2"/>
     </row>
@@ -15440,7 +15440,7 @@
         <v>1026</v>
       </c>
       <c r="E100" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F100" s="2"/>
     </row>
@@ -15558,7 +15558,7 @@
         <v>1026</v>
       </c>
       <c r="E106" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -15596,7 +15596,7 @@
         <v>1026</v>
       </c>
       <c r="E108" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F108" s="2"/>
     </row>
@@ -15774,7 +15774,7 @@
         <v>1026</v>
       </c>
       <c r="E117" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -15872,7 +15872,7 @@
         <v>1026</v>
       </c>
       <c r="E122" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -15890,7 +15890,7 @@
         <v>1026</v>
       </c>
       <c r="E123" s="2">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -15926,7 +15926,7 @@
         <v>1026</v>
       </c>
       <c r="E125" s="2">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -15944,7 +15944,7 @@
         <v>1026</v>
       </c>
       <c r="E126" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -15962,7 +15962,7 @@
         <v>1026</v>
       </c>
       <c r="E127" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -15980,7 +15980,7 @@
         <v>1026</v>
       </c>
       <c r="E128" s="2">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -15998,7 +15998,7 @@
         <v>1026</v>
       </c>
       <c r="E129" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -16016,7 +16016,7 @@
         <v>1026</v>
       </c>
       <c r="E130" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -16034,7 +16034,7 @@
         <v>1026</v>
       </c>
       <c r="E131" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -16052,7 +16052,7 @@
         <v>1026</v>
       </c>
       <c r="E132" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -16088,7 +16088,7 @@
         <v>1026</v>
       </c>
       <c r="E134" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F134" s="2"/>
     </row>
@@ -16106,7 +16106,7 @@
         <v>1026</v>
       </c>
       <c r="E135" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F135" s="2"/>
     </row>
@@ -16124,7 +16124,7 @@
         <v>1026</v>
       </c>
       <c r="E136" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F136" s="2"/>
     </row>
@@ -16142,7 +16142,7 @@
         <v>1026</v>
       </c>
       <c r="E137" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F137" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/09-report/CYC-2-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/09-report/CYC-2-cycle-report.xlsx
@@ -169,7 +169,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T19:27:33.764Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T19:43:47.135Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -4566,7 +4566,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T19:27:34.533Z</t>
+    <t>2026-10-02T19:43:47.934Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -20402,7 +20402,7 @@
         <v>1028</v>
       </c>
       <c r="E2" s="2">
-        <v>518</v>
+        <v>543</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -20520,7 +20520,7 @@
         <v>1028</v>
       </c>
       <c r="E8" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -20556,7 +20556,7 @@
         <v>1028</v>
       </c>
       <c r="E10" s="2">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -20574,7 +20574,7 @@
         <v>1028</v>
       </c>
       <c r="E11" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -20592,7 +20592,7 @@
         <v>1028</v>
       </c>
       <c r="E12" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -20688,7 +20688,7 @@
         <v>1028</v>
       </c>
       <c r="E17" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -20706,7 +20706,7 @@
         <v>1028</v>
       </c>
       <c r="E18" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -20784,7 +20784,7 @@
         <v>1028</v>
       </c>
       <c r="E22" s="2">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="F22" s="2"/>
     </row>
@@ -20822,7 +20822,7 @@
         <v>1028</v>
       </c>
       <c r="E24" s="2">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -20840,7 +20840,7 @@
         <v>1028</v>
       </c>
       <c r="E25" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -20858,7 +20858,7 @@
         <v>1028</v>
       </c>
       <c r="E26" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -20876,7 +20876,7 @@
         <v>1028</v>
       </c>
       <c r="E27" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -20894,7 +20894,7 @@
         <v>1028</v>
       </c>
       <c r="E28" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -20912,7 +20912,7 @@
         <v>1028</v>
       </c>
       <c r="E29" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -20930,7 +20930,7 @@
         <v>1028</v>
       </c>
       <c r="E30" s="2">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -20966,7 +20966,7 @@
         <v>1028</v>
       </c>
       <c r="E32" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F32" s="2"/>
     </row>
@@ -21022,7 +21022,7 @@
         <v>1028</v>
       </c>
       <c r="E35" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F35" s="2"/>
     </row>
@@ -21080,7 +21080,7 @@
         <v>1028</v>
       </c>
       <c r="E38" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F38" s="2"/>
     </row>
@@ -21118,7 +21118,7 @@
         <v>1028</v>
       </c>
       <c r="E40" s="2">
-        <v>146</v>
+        <v>196</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -21234,7 +21234,7 @@
         <v>1028</v>
       </c>
       <c r="E46" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -21252,7 +21252,7 @@
         <v>1028</v>
       </c>
       <c r="E47" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -21270,7 +21270,7 @@
         <v>1028</v>
       </c>
       <c r="E48" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F48" s="2"/>
     </row>
@@ -21308,7 +21308,7 @@
         <v>1028</v>
       </c>
       <c r="E50" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -21326,7 +21326,7 @@
         <v>1028</v>
       </c>
       <c r="E51" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -21344,7 +21344,7 @@
         <v>1028</v>
       </c>
       <c r="E52" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F52" s="2"/>
     </row>
@@ -21462,7 +21462,7 @@
         <v>1028</v>
       </c>
       <c r="E58" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -21480,7 +21480,7 @@
         <v>1028</v>
       </c>
       <c r="E59" s="2">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F59" s="2"/>
     </row>
@@ -21518,7 +21518,7 @@
         <v>1028</v>
       </c>
       <c r="E61" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F61" s="2"/>
     </row>
@@ -21616,7 +21616,7 @@
         <v>1028</v>
       </c>
       <c r="E66" s="2">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -21634,7 +21634,7 @@
         <v>1028</v>
       </c>
       <c r="E67" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -21652,7 +21652,7 @@
         <v>1028</v>
       </c>
       <c r="E68" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F68" s="2"/>
     </row>
@@ -21710,7 +21710,7 @@
         <v>1028</v>
       </c>
       <c r="E71" s="2">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -21728,7 +21728,7 @@
         <v>1028</v>
       </c>
       <c r="E72" s="2">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -21746,7 +21746,7 @@
         <v>1028</v>
       </c>
       <c r="E73" s="2">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F73" s="2"/>
     </row>
@@ -21784,7 +21784,7 @@
         <v>1028</v>
       </c>
       <c r="E75" s="2">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -21802,7 +21802,7 @@
         <v>1028</v>
       </c>
       <c r="E76" s="2">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -21820,7 +21820,7 @@
         <v>1028</v>
       </c>
       <c r="E77" s="2">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -21838,7 +21838,7 @@
         <v>1028</v>
       </c>
       <c r="E78" s="2">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="F78" s="2"/>
     </row>
@@ -21896,7 +21896,7 @@
         <v>1028</v>
       </c>
       <c r="E81" s="2">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -21914,7 +21914,7 @@
         <v>1028</v>
       </c>
       <c r="E82" s="2">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -21932,7 +21932,7 @@
         <v>1028</v>
       </c>
       <c r="E83" s="2">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="F83" s="2"/>
     </row>
@@ -22010,7 +22010,7 @@
         <v>1028</v>
       </c>
       <c r="E87" s="2">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -22028,7 +22028,7 @@
         <v>1028</v>
       </c>
       <c r="E88" s="2">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -22046,7 +22046,7 @@
         <v>1028</v>
       </c>
       <c r="E89" s="2">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -22064,7 +22064,7 @@
         <v>1028</v>
       </c>
       <c r="E90" s="2">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -22082,7 +22082,7 @@
         <v>1028</v>
       </c>
       <c r="E91" s="2">
-        <v>49</v>
+        <v>158</v>
       </c>
       <c r="F91" s="2"/>
     </row>
@@ -22140,7 +22140,7 @@
         <v>1028</v>
       </c>
       <c r="E94" s="2">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -22178,7 +22178,7 @@
         <v>1028</v>
       </c>
       <c r="E96" s="2">
-        <v>141</v>
+        <v>215</v>
       </c>
       <c r="F96" s="2"/>
     </row>
@@ -22256,7 +22256,7 @@
         <v>1028</v>
       </c>
       <c r="E100" s="2">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="F100" s="2"/>
     </row>
@@ -22374,7 +22374,7 @@
         <v>1028</v>
       </c>
       <c r="E106" s="2">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -22412,7 +22412,7 @@
         <v>1028</v>
       </c>
       <c r="E108" s="2">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="F108" s="2"/>
     </row>
@@ -22590,7 +22590,7 @@
         <v>1028</v>
       </c>
       <c r="E117" s="2">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -22688,7 +22688,7 @@
         <v>1028</v>
       </c>
       <c r="E122" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -22706,7 +22706,7 @@
         <v>1028</v>
       </c>
       <c r="E123" s="2">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -22724,7 +22724,7 @@
         <v>1028</v>
       </c>
       <c r="E124" s="2">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -22742,7 +22742,7 @@
         <v>1028</v>
       </c>
       <c r="E125" s="2">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -22760,7 +22760,7 @@
         <v>1028</v>
       </c>
       <c r="E126" s="2">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -22778,7 +22778,7 @@
         <v>1028</v>
       </c>
       <c r="E127" s="2">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -22796,7 +22796,7 @@
         <v>1028</v>
       </c>
       <c r="E128" s="2">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -22814,7 +22814,7 @@
         <v>1028</v>
       </c>
       <c r="E129" s="2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -22832,7 +22832,7 @@
         <v>1028</v>
       </c>
       <c r="E130" s="2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -22850,7 +22850,7 @@
         <v>1028</v>
       </c>
       <c r="E131" s="2">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -22868,7 +22868,7 @@
         <v>1028</v>
       </c>
       <c r="E132" s="2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -22886,7 +22886,7 @@
         <v>1028</v>
       </c>
       <c r="E133" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F133" s="2"/>
     </row>
@@ -22904,7 +22904,7 @@
         <v>1028</v>
       </c>
       <c r="E134" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F134" s="2"/>
     </row>
@@ -22922,7 +22922,7 @@
         <v>1028</v>
       </c>
       <c r="E135" s="2">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F135" s="2"/>
     </row>
@@ -22940,7 +22940,7 @@
         <v>1028</v>
       </c>
       <c r="E136" s="2">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F136" s="2"/>
     </row>
@@ -22958,7 +22958,7 @@
         <v>1028</v>
       </c>
       <c r="E137" s="2">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F137" s="2"/>
     </row>
@@ -22976,7 +22976,7 @@
         <v>1028</v>
       </c>
       <c r="E138" s="2">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F138" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/09-report/CYC-2-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/09-report/CYC-2-cycle-report.xlsx
@@ -10,20 +10,21 @@
     <sheet sheetId="4" name="Test Cases" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Execution" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="Defects" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Coverage" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Attribute coverage" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Traceability by story" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Traceability matrix" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Approvals" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="Skills" state="visible" r:id="rId15"/>
-    <sheet sheetId="13" name="Hand-overs" state="visible" r:id="rId16"/>
+    <sheet sheetId="7" name="Fixed and certified" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Coverage" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Attribute coverage" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Traceability by story" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Traceability matrix" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Approvals" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Skills" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="Hand-overs" state="visible" r:id="rId17"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5768" uniqueCount="1584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5810" uniqueCount="1604">
   <si>
     <t>Metric</t>
   </si>
@@ -115,7 +116,7 @@
     <t>Narrative</t>
   </si>
   <si>
-    <t>Hotel booking baseline · Regression (baseline) worked from Jira initiative AQPI-1 (Jira export on GitHub), Jira epic AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) (pulled live from GitHub). The reviewed requirement set holds 128 requirements. 137 test cases are designed, 74 of them automated in 58 Playwright scripts. Execution ran 74 automated cases for real: 74 passed and 0 failed (pass rate 100%). No defects were raised.</t>
+    <t>Hotel booking baseline · Regression (baseline) worked from Jira initiative AQPI-1 (Jira export on GitHub), Jira epic AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) (pulled live from GitHub). The reviewed requirement set holds 128 requirements. 137 test cases are designed, 74 of them automated in 58 Playwright scripts. Execution ran 74 automated cases for real: 71 passed and 3 failed (pass rate 95.9%). 3 defect(s) were raised from real failures: DEF-004 A price change within 1% does not need acknowledgement: returns true instead of false; DEF-005 A key shorter than 8 characters is refused: returns 201 instead of 400; DEF-006 9 rooms in one search are rejected: returns 200 instead of 400.</t>
   </si>
   <si>
     <t>Narrative drafted by</t>
@@ -163,13 +164,13 @@
     <t>Codebase</t>
   </si>
   <si>
-    <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef)</t>
+    <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41)</t>
   </si>
   <si>
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T19:43:47.135Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-02T20:04:55.461Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -2857,7 +2858,7 @@
     <t>expiresAt - createdAt = 30 min; timeout behaviour shown; no reservation exists</t>
   </si>
   <si>
-    <t>cart-service/src/main/resources/cart-service.yml, REQ-122, BR-122</t>
+    <t>AQPI-15, REQ-122, BR-122</t>
   </si>
   <si>
     <t>TC-F-113</t>
@@ -2883,7 +2884,7 @@
     <t>Revalidation requires acknowledgement; first submit HTTP 409 PRICE_CHANGE_REQUIRES_ACKNOWLEDGEMENT; after acknowledging HTTP 201</t>
   </si>
   <si>
-    <t>cart-service/src/main/resources/cart-service.yml, REQ-123, BR-123</t>
+    <t>AQPI-17, REQ-123, BR-123</t>
   </si>
   <si>
     <t>TC-F-114</t>
@@ -2922,7 +2923,7 @@
     <t>First 3 resends HTTP 202, the next HTTP 429; still one reservation</t>
   </si>
   <si>
-    <t>notification-service/src/main/resources/notification-service.yml, REQ-124, BR-124</t>
+    <t>AQPI-26, REQ-124, BR-124</t>
   </si>
   <si>
     <t>TC-F-116</t>
@@ -2941,7 +2942,7 @@
     <t>HTTP 400 IDEMPOTENCY_KEY_REQUIRED</t>
   </si>
   <si>
-    <t>reservation-service/src/main/resources/reservation-service.yml, REQ-125, BR-125</t>
+    <t>AQPI-21, REQ-125, BR-125</t>
   </si>
   <si>
     <t>TC-F-117</t>
@@ -2991,7 +2992,7 @@
     <t>HTTP 200 with a searchId</t>
   </si>
   <si>
-    <t>search-service/src/main/resources/search-service.yml, REQ-126, BR-126</t>
+    <t>AQPI-4, REQ-126, BR-126</t>
   </si>
   <si>
     <t>TC-F-120</t>
@@ -3057,7 +3058,7 @@
     <t>occupancy.adults=4; every other booking attribute from the hotel data dictionary examples</t>
   </si>
   <si>
-    <t>search-service/src/main/resources/search-service.yml, REQ-127, BR-127</t>
+    <t>AQPI-4, REQ-127, BR-127</t>
   </si>
   <si>
     <t>TC-F-124</t>
@@ -3129,7 +3130,7 @@
     <t>stay.checkInOffsetDays=500; every other booking attribute from the hotel data dictionary examples</t>
   </si>
   <si>
-    <t>search-service/src/main/resources/search-service.yml, REQ-128, BR-128</t>
+    <t>AQPI-4, REQ-128, BR-128</t>
   </si>
   <si>
     <t>TC-F-128</t>
@@ -3171,6 +3172,9 @@
     <t>Manual test case - not automated, not executed</t>
   </si>
   <si>
+    <t>failed</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -3195,6 +3199,75 @@
     <t>Movement</t>
   </si>
   <si>
+    <t>DEF-004</t>
+  </si>
+  <si>
+    <t>A price change within 1% does not need acknowledgement: returns true instead of false</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>AQPI-17</t>
+  </si>
+  <si>
+    <t>not raised in Jira; linked to AQPI-17 in the platform</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>expect(rv.body.requiresAcknowledgement).toBe(false);</t>
+  </si>
+  <si>
+    <t>DEF-005</t>
+  </si>
+  <si>
+    <t>A key shorter than 8 characters is refused: returns 201 instead of 400</t>
+  </si>
+  <si>
+    <t>AQPI-21</t>
+  </si>
+  <si>
+    <t>not raised in Jira; linked to AQPI-21 in the platform</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>expect(r.status).toBe(400);</t>
+  </si>
+  <si>
+    <t>DEF-006</t>
+  </si>
+  <si>
+    <t>9 rooms in one search are rejected: returns 200 instead of 400</t>
+  </si>
+  <si>
+    <t>AQPI-4</t>
+  </si>
+  <si>
+    <t>not raised in Jira; linked to AQPI-4 in the platform</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>First seen</t>
+  </si>
+  <si>
+    <t>Retested in</t>
+  </si>
+  <si>
+    <t>Certification</t>
+  </si>
+  <si>
     <t>Text</t>
   </si>
   <si>
@@ -3213,6 +3286,9 @@
     <t>designed only (manual)</t>
   </si>
   <si>
+    <t>executed - failing</t>
+  </si>
+  <si>
     <t>Attribute</t>
   </si>
   <si>
@@ -3261,6 +3337,9 @@
     <t>TC-F-016, TC-F-126</t>
   </si>
   <si>
+    <t>exercised - failing</t>
+  </si>
+  <si>
     <t>occupancy.adults</t>
   </si>
   <si>
@@ -3390,12 +3469,12 @@
     <t>3.1 Search hotels by destination and date range</t>
   </si>
   <si>
-    <t>AQPI-4</t>
-  </si>
-  <si>
     <t>3.2 Validate occupancy and stay criteria</t>
   </si>
   <si>
+    <t>failing</t>
+  </si>
+  <si>
     <t>AQPI-5</t>
   </si>
   <si>
@@ -3468,9 +3547,6 @@
     <t>6.2 Add, update, and remove ancillaries</t>
   </si>
   <si>
-    <t>AQPI-17</t>
-  </si>
-  <si>
     <t>6.3 Review cart and total price</t>
   </si>
   <si>
@@ -3492,9 +3568,6 @@
     <t>7.2 Capture and authorize payment</t>
   </si>
   <si>
-    <t>AQPI-21</t>
-  </si>
-  <si>
     <t>7.3 Create reservation idempotently</t>
   </si>
   <si>
@@ -4437,9 +4510,6 @@
     <t>TD-F-111</t>
   </si>
   <si>
-    <t>cart-service/src/main/resources/cart-service.yml</t>
-  </si>
-  <si>
     <t>BR-122</t>
   </si>
   <si>
@@ -4461,9 +4531,6 @@
     <t>TD-F-114</t>
   </si>
   <si>
-    <t>notification-service/src/main/resources/notification-service.yml</t>
-  </si>
-  <si>
     <t>BR-124</t>
   </si>
   <si>
@@ -4473,9 +4540,6 @@
     <t>br-124-resend-limit.spec.js</t>
   </si>
   <si>
-    <t>reservation-service/src/main/resources/reservation-service.yml</t>
-  </si>
-  <si>
     <t>BR-125</t>
   </si>
   <si>
@@ -4491,9 +4555,6 @@
     <t>TD-F-118</t>
   </si>
   <si>
-    <t>search-service/src/main/resources/search-service.yml</t>
-  </si>
-  <si>
     <t>BR-126</t>
   </si>
   <si>
@@ -4566,7 +4627,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T19:43:47.934Z</t>
+    <t>2026-10-02T20:04:56.274Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -5333,7 +5394,7 @@
         <v>22</v>
       </c>
       <c r="B14" s="2">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5341,7 +5402,7 @@
         <v>23</v>
       </c>
       <c r="B15" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5349,7 +5410,7 @@
         <v>24</v>
       </c>
       <c r="B16" s="2">
-        <v>100</v>
+        <v>95.9</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5365,7 +5426,7 @@
         <v>27</v>
       </c>
       <c r="B18" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5373,7 +5434,7 @@
         <v>28</v>
       </c>
       <c r="B19" s="2">
-        <v>45.3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5399,6 +5460,1146 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K32"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="9" width="8" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E3" s="2">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E4" s="2">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2">
+        <v>9</v>
+      </c>
+      <c r="G4" s="2">
+        <v>6</v>
+      </c>
+      <c r="H4" s="2">
+        <v>6</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E5" s="2">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2">
+        <v>12</v>
+      </c>
+      <c r="H5" s="2">
+        <v>11</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2</v>
+      </c>
+      <c r="H6" s="2">
+        <v>2</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2">
+        <v>5</v>
+      </c>
+      <c r="G8" s="2">
+        <v>5</v>
+      </c>
+      <c r="H8" s="2">
+        <v>5</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2">
+        <v>5</v>
+      </c>
+      <c r="G9" s="2">
+        <v>4</v>
+      </c>
+      <c r="H9" s="2">
+        <v>4</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2">
+        <v>4</v>
+      </c>
+      <c r="G10" s="2">
+        <v>2</v>
+      </c>
+      <c r="H10" s="2">
+        <v>2</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2">
+        <v>4</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E12" s="2">
+        <v>7</v>
+      </c>
+      <c r="F12" s="2">
+        <v>7</v>
+      </c>
+      <c r="G12" s="2">
+        <v>2</v>
+      </c>
+      <c r="H12" s="2">
+        <v>2</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2">
+        <v>3</v>
+      </c>
+      <c r="H13" s="2">
+        <v>3</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E14" s="2">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2">
+        <v>3</v>
+      </c>
+      <c r="G14" s="2">
+        <v>2</v>
+      </c>
+      <c r="H14" s="2">
+        <v>2</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E15" s="2">
+        <v>4</v>
+      </c>
+      <c r="F15" s="2">
+        <v>4</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E16" s="2">
+        <v>6</v>
+      </c>
+      <c r="F16" s="2">
+        <v>6</v>
+      </c>
+      <c r="G16" s="2">
+        <v>2</v>
+      </c>
+      <c r="H16" s="2">
+        <v>2</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E17" s="2">
+        <v>4</v>
+      </c>
+      <c r="F17" s="2">
+        <v>4</v>
+      </c>
+      <c r="G17" s="2">
+        <v>2</v>
+      </c>
+      <c r="H17" s="2">
+        <v>2</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E18" s="2">
+        <v>6</v>
+      </c>
+      <c r="F18" s="2">
+        <v>7</v>
+      </c>
+      <c r="G18" s="2">
+        <v>3</v>
+      </c>
+      <c r="H18" s="2">
+        <v>2</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E19" s="2">
+        <v>4</v>
+      </c>
+      <c r="F19" s="2">
+        <v>4</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E20" s="2">
+        <v>6</v>
+      </c>
+      <c r="F20" s="2">
+        <v>6</v>
+      </c>
+      <c r="G20" s="2">
+        <v>4</v>
+      </c>
+      <c r="H20" s="2">
+        <v>4</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E21" s="2">
+        <v>6</v>
+      </c>
+      <c r="F21" s="2">
+        <v>9</v>
+      </c>
+      <c r="G21" s="2">
+        <v>6</v>
+      </c>
+      <c r="H21" s="2">
+        <v>6</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E22" s="2">
+        <v>7</v>
+      </c>
+      <c r="F22" s="2">
+        <v>9</v>
+      </c>
+      <c r="G22" s="2">
+        <v>6</v>
+      </c>
+      <c r="H22" s="2">
+        <v>5</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E23" s="2">
+        <v>3</v>
+      </c>
+      <c r="F23" s="2">
+        <v>3</v>
+      </c>
+      <c r="G23" s="2">
+        <v>3</v>
+      </c>
+      <c r="H23" s="2">
+        <v>3</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E24" s="2">
+        <v>4</v>
+      </c>
+      <c r="F24" s="2">
+        <v>4</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E25" s="2">
+        <v>5</v>
+      </c>
+      <c r="F25" s="2">
+        <v>5</v>
+      </c>
+      <c r="G25" s="2">
+        <v>3</v>
+      </c>
+      <c r="H25" s="2">
+        <v>3</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E26" s="2">
+        <v>5</v>
+      </c>
+      <c r="F26" s="2">
+        <v>5</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2">
+        <v>1</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E27" s="2">
+        <v>4</v>
+      </c>
+      <c r="F27" s="2">
+        <v>4</v>
+      </c>
+      <c r="G27" s="2">
+        <v>2</v>
+      </c>
+      <c r="H27" s="2">
+        <v>2</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E28" s="2">
+        <v>4</v>
+      </c>
+      <c r="F28" s="2">
+        <v>4</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E29" s="2">
+        <v>5</v>
+      </c>
+      <c r="F29" s="2">
+        <v>5</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2">
+        <v>1</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E30" s="2">
+        <v>6</v>
+      </c>
+      <c r="F30" s="2">
+        <v>6</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1</v>
+      </c>
+      <c r="H30" s="2">
+        <v>1</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E31" s="2">
+        <v>4</v>
+      </c>
+      <c r="F31" s="2">
+        <v>4</v>
+      </c>
+      <c r="G31" s="2">
+        <v>1</v>
+      </c>
+      <c r="H31" s="2">
+        <v>1</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E32" s="2">
+        <v>4</v>
+      </c>
+      <c r="F32" s="2">
+        <v>4</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M138"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -5418,19 +6619,19 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1160</v>
+        <v>1184</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1161</v>
+        <v>1185</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1162</v>
+        <v>1186</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1163</v>
+        <v>1187</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>314</v>
@@ -5439,22 +6640,22 @@
         <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1164</v>
+        <v>1188</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1165</v>
+        <v>1189</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1166</v>
+        <v>1190</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>1025</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1167</v>
+        <v>1191</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5468,7 +6669,7 @@
         <v>61</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1168</v>
+        <v>1192</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>326</v>
@@ -5483,10 +6684,10 @@
         <v>337</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>1169</v>
+        <v>1193</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>1170</v>
+        <v>1194</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>1028</v>
@@ -5509,7 +6710,7 @@
         <v>71</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1171</v>
+        <v>1195</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>340</v>
@@ -5524,7 +6725,7 @@
         <v>348</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1172</v>
+        <v>1196</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
@@ -5548,7 +6749,7 @@
         <v>73</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1173</v>
+        <v>1197</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>349</v>
@@ -5563,7 +6764,7 @@
         <v>348</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1174</v>
+        <v>1198</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
@@ -5587,7 +6788,7 @@
         <v>75</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1175</v>
+        <v>1199</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>353</v>
@@ -5602,7 +6803,7 @@
         <v>348</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1176</v>
+        <v>1200</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
@@ -5626,7 +6827,7 @@
         <v>77</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1177</v>
+        <v>1201</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>357</v>
@@ -5641,7 +6842,7 @@
         <v>348</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1178</v>
+        <v>1202</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
@@ -5665,7 +6866,7 @@
         <v>79</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1179</v>
+        <v>1203</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>361</v>
@@ -5680,7 +6881,7 @@
         <v>348</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1180</v>
+        <v>1204</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
@@ -5695,7 +6896,7 @@
     </row>
     <row r="8" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1101</v>
+        <v>1127</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>80</v>
@@ -5704,7 +6905,7 @@
         <v>81</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1181</v>
+        <v>1205</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>365</v>
@@ -5719,10 +6920,10 @@
         <v>337</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1182</v>
+        <v>1206</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1183</v>
+        <v>1207</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>1028</v>
@@ -5736,7 +6937,7 @@
     </row>
     <row r="9" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1101</v>
+        <v>1127</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>82</v>
@@ -5745,7 +6946,7 @@
         <v>83</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1184</v>
+        <v>1208</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>373</v>
@@ -5760,10 +6961,10 @@
         <v>337</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1185</v>
+        <v>1209</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1186</v>
+        <v>1210</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>1028</v>
@@ -5777,7 +6978,7 @@
     </row>
     <row r="10" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1101</v>
+        <v>1127</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>84</v>
@@ -5786,7 +6987,7 @@
         <v>85</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1187</v>
+        <v>1211</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>379</v>
@@ -5801,10 +7002,10 @@
         <v>337</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1188</v>
+        <v>1212</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1189</v>
+        <v>1213</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>1028</v>
@@ -5818,7 +7019,7 @@
     </row>
     <row r="11" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1101</v>
+        <v>1127</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>84</v>
@@ -5827,7 +7028,7 @@
         <v>85</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1187</v>
+        <v>1211</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>386</v>
@@ -5842,10 +7043,10 @@
         <v>337</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1190</v>
+        <v>1214</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1189</v>
+        <v>1213</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>1028</v>
@@ -5859,7 +7060,7 @@
     </row>
     <row r="12" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1101</v>
+        <v>1127</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>84</v>
@@ -5868,7 +7069,7 @@
         <v>85</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1187</v>
+        <v>1211</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>392</v>
@@ -5883,10 +7084,10 @@
         <v>337</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>1191</v>
+        <v>1215</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1189</v>
+        <v>1213</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>1028</v>
@@ -5900,7 +7101,7 @@
     </row>
     <row r="13" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1101</v>
+        <v>1127</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>86</v>
@@ -5909,7 +7110,7 @@
         <v>87</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1192</v>
+        <v>1216</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>398</v>
@@ -5924,10 +7125,10 @@
         <v>337</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>1193</v>
+        <v>1217</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1194</v>
+        <v>1218</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>1028</v>
@@ -5941,7 +7142,7 @@
     </row>
     <row r="14" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1101</v>
+        <v>1127</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>89</v>
@@ -5950,7 +7151,7 @@
         <v>90</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1195</v>
+        <v>1219</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>407</v>
@@ -5965,7 +7166,7 @@
         <v>348</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>1196</v>
+        <v>1220</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
@@ -5980,7 +7181,7 @@
     </row>
     <row r="15" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1101</v>
+        <v>1127</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>91</v>
@@ -5989,7 +7190,7 @@
         <v>92</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1197</v>
+        <v>1221</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>411</v>
@@ -6004,7 +7205,7 @@
         <v>348</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1198</v>
+        <v>1222</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
@@ -6019,7 +7220,7 @@
     </row>
     <row r="16" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>1101</v>
+        <v>1127</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>93</v>
@@ -6028,7 +7229,7 @@
         <v>94</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1199</v>
+        <v>1223</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>415</v>
@@ -6043,7 +7244,7 @@
         <v>348</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1200</v>
+        <v>1224</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
@@ -6058,7 +7259,7 @@
     </row>
     <row r="17" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>1104</v>
+        <v>1057</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>95</v>
@@ -6067,7 +7268,7 @@
         <v>96</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1201</v>
+        <v>1225</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>419</v>
@@ -6082,10 +7283,10 @@
         <v>337</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>1202</v>
+        <v>1226</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>1203</v>
+        <v>1227</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>1028</v>
@@ -6099,7 +7300,7 @@
     </row>
     <row r="18" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>1104</v>
+        <v>1057</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>97</v>
@@ -6108,7 +7309,7 @@
         <v>98</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1204</v>
+        <v>1228</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>425</v>
@@ -6123,10 +7324,10 @@
         <v>337</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>1205</v>
+        <v>1229</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>1206</v>
+        <v>1230</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>1028</v>
@@ -6140,7 +7341,7 @@
     </row>
     <row r="19" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>1104</v>
+        <v>1057</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>99</v>
@@ -6149,7 +7350,7 @@
         <v>100</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1207</v>
+        <v>1231</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>432</v>
@@ -6164,7 +7365,7 @@
         <v>348</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>1208</v>
+        <v>1232</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
@@ -6179,7 +7380,7 @@
     </row>
     <row r="20" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>1104</v>
+        <v>1057</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>101</v>
@@ -6188,7 +7389,7 @@
         <v>102</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1209</v>
+        <v>1233</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>436</v>
@@ -6203,7 +7404,7 @@
         <v>348</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>1210</v>
+        <v>1234</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
@@ -6218,7 +7419,7 @@
     </row>
     <row r="21" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>1104</v>
+        <v>1057</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>103</v>
@@ -6227,7 +7428,7 @@
         <v>104</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1211</v>
+        <v>1235</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>440</v>
@@ -6242,7 +7443,7 @@
         <v>348</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>1212</v>
+        <v>1236</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2" t="s">
@@ -6257,7 +7458,7 @@
     </row>
     <row r="22" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>1106</v>
+        <v>1132</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>105</v>
@@ -6266,7 +7467,7 @@
         <v>106</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1213</v>
+        <v>1237</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>444</v>
@@ -6281,10 +7482,10 @@
         <v>337</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>1214</v>
+        <v>1238</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>1215</v>
+        <v>1239</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>1028</v>
@@ -6298,7 +7499,7 @@
     </row>
     <row r="23" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>1106</v>
+        <v>1132</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>107</v>
@@ -6307,7 +7508,7 @@
         <v>108</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1216</v>
+        <v>1240</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>446</v>
@@ -6322,7 +7523,7 @@
         <v>348</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>1217</v>
+        <v>1241</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
@@ -6337,7 +7538,7 @@
     </row>
     <row r="24" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>1106</v>
+        <v>1132</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>109</v>
@@ -6346,7 +7547,7 @@
         <v>110</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1218</v>
+        <v>1242</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>450</v>
@@ -6361,10 +7562,10 @@
         <v>337</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>1219</v>
+        <v>1243</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>1220</v>
+        <v>1244</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>1028</v>
@@ -6378,7 +7579,7 @@
     </row>
     <row r="25" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>1110</v>
+        <v>1136</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>111</v>
@@ -6387,7 +7588,7 @@
         <v>112</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1221</v>
+        <v>1245</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>456</v>
@@ -6402,10 +7603,10 @@
         <v>337</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>1222</v>
+        <v>1246</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>1223</v>
+        <v>1247</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>1028</v>
@@ -6419,7 +7620,7 @@
     </row>
     <row r="26" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>1110</v>
+        <v>1136</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>113</v>
@@ -6428,7 +7629,7 @@
         <v>114</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1224</v>
+        <v>1248</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>462</v>
@@ -6443,10 +7644,10 @@
         <v>337</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>1225</v>
+        <v>1249</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>1226</v>
+        <v>1250</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>1028</v>
@@ -6460,7 +7661,7 @@
     </row>
     <row r="27" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>1110</v>
+        <v>1136</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>115</v>
@@ -6469,7 +7670,7 @@
         <v>116</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1227</v>
+        <v>1251</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>467</v>
@@ -6484,10 +7685,10 @@
         <v>337</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>1228</v>
+        <v>1252</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>1229</v>
+        <v>1253</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>1028</v>
@@ -6501,7 +7702,7 @@
     </row>
     <row r="28" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>1110</v>
+        <v>1136</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>117</v>
@@ -6510,7 +7711,7 @@
         <v>118</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1230</v>
+        <v>1254</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>475</v>
@@ -6525,10 +7726,10 @@
         <v>337</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>1231</v>
+        <v>1255</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>1232</v>
+        <v>1256</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>1028</v>
@@ -6542,7 +7743,7 @@
     </row>
     <row r="29" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>1110</v>
+        <v>1136</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>119</v>
@@ -6551,7 +7752,7 @@
         <v>120</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1233</v>
+        <v>1257</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>481</v>
@@ -6566,10 +7767,10 @@
         <v>337</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>1234</v>
+        <v>1258</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>1235</v>
+        <v>1259</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>1028</v>
@@ -6583,7 +7784,7 @@
     </row>
     <row r="30" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>1112</v>
+        <v>1138</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>121</v>
@@ -6592,7 +7793,7 @@
         <v>122</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1236</v>
+        <v>1260</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>488</v>
@@ -6607,10 +7808,10 @@
         <v>337</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>1237</v>
+        <v>1261</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>1238</v>
+        <v>1262</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>1028</v>
@@ -6624,7 +7825,7 @@
     </row>
     <row r="31" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>1112</v>
+        <v>1138</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>123</v>
@@ -6633,7 +7834,7 @@
         <v>124</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1239</v>
+        <v>1263</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>494</v>
@@ -6648,10 +7849,10 @@
         <v>337</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>1240</v>
+        <v>1264</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>1241</v>
+        <v>1265</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>1028</v>
@@ -6665,7 +7866,7 @@
     </row>
     <row r="32" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>1112</v>
+        <v>1138</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>123</v>
@@ -6674,7 +7875,7 @@
         <v>124</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1239</v>
+        <v>1263</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>500</v>
@@ -6689,10 +7890,10 @@
         <v>337</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1242</v>
+        <v>1266</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>1241</v>
+        <v>1265</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>1028</v>
@@ -6706,7 +7907,7 @@
     </row>
     <row r="33" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>1112</v>
+        <v>1138</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>125</v>
@@ -6715,7 +7916,7 @@
         <v>126</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1243</v>
+        <v>1267</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>505</v>
@@ -6730,7 +7931,7 @@
         <v>348</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>1244</v>
+        <v>1268</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
@@ -6745,7 +7946,7 @@
     </row>
     <row r="34" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>1112</v>
+        <v>1138</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>127</v>
@@ -6754,7 +7955,7 @@
         <v>128</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1245</v>
+        <v>1269</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>509</v>
@@ -6769,10 +7970,10 @@
         <v>337</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>1246</v>
+        <v>1270</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>1247</v>
+        <v>1271</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>1028</v>
@@ -6786,7 +7987,7 @@
     </row>
     <row r="35" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>1114</v>
+        <v>1140</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>129</v>
@@ -6795,7 +7996,7 @@
         <v>130</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1248</v>
+        <v>1272</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>515</v>
@@ -6810,10 +8011,10 @@
         <v>337</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>1249</v>
+        <v>1273</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>1250</v>
+        <v>1274</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>1028</v>
@@ -6827,7 +8028,7 @@
     </row>
     <row r="36" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>1114</v>
+        <v>1140</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>131</v>
@@ -6836,7 +8037,7 @@
         <v>132</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1251</v>
+        <v>1275</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>521</v>
@@ -6851,7 +8052,7 @@
         <v>348</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>1252</v>
+        <v>1276</v>
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
@@ -6866,7 +8067,7 @@
     </row>
     <row r="37" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>1114</v>
+        <v>1140</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>133</v>
@@ -6875,7 +8076,7 @@
         <v>134</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1253</v>
+        <v>1277</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>525</v>
@@ -6890,7 +8091,7 @@
         <v>348</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>1254</v>
+        <v>1278</v>
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
@@ -6905,7 +8106,7 @@
     </row>
     <row r="38" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>1114</v>
+        <v>1140</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>135</v>
@@ -6914,7 +8115,7 @@
         <v>136</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1255</v>
+        <v>1279</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>529</v>
@@ -6929,10 +8130,10 @@
         <v>337</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>1256</v>
+        <v>1280</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>1257</v>
+        <v>1281</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>1028</v>
@@ -6946,7 +8147,7 @@
     </row>
     <row r="39" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>1118</v>
+        <v>1144</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>137</v>
@@ -6955,7 +8156,7 @@
         <v>138</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1258</v>
+        <v>1282</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>535</v>
@@ -6970,7 +8171,7 @@
         <v>348</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>1259</v>
+        <v>1283</v>
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
@@ -6985,7 +8186,7 @@
     </row>
     <row r="40" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>1118</v>
+        <v>1144</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>139</v>
@@ -6994,7 +8195,7 @@
         <v>140</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1260</v>
+        <v>1284</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>539</v>
@@ -7009,10 +8210,10 @@
         <v>337</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>1261</v>
+        <v>1285</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>1262</v>
+        <v>1286</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>1028</v>
@@ -7026,7 +8227,7 @@
     </row>
     <row r="41" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>1118</v>
+        <v>1144</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>141</v>
@@ -7035,7 +8236,7 @@
         <v>142</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1263</v>
+        <v>1287</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>545</v>
@@ -7050,10 +8251,10 @@
         <v>337</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>1264</v>
+        <v>1288</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>1265</v>
+        <v>1289</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>1028</v>
@@ -7067,7 +8268,7 @@
     </row>
     <row r="42" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>1118</v>
+        <v>1144</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>143</v>
@@ -7076,7 +8277,7 @@
         <v>144</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1266</v>
+        <v>1290</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>551</v>
@@ -7091,7 +8292,7 @@
         <v>348</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>1267</v>
+        <v>1291</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
@@ -7106,7 +8307,7 @@
     </row>
     <row r="43" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>1118</v>
+        <v>1144</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>145</v>
@@ -7115,7 +8316,7 @@
         <v>146</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1268</v>
+        <v>1292</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>555</v>
@@ -7130,7 +8331,7 @@
         <v>348</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>1269</v>
+        <v>1293</v>
       </c>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
@@ -7145,7 +8346,7 @@
     </row>
     <row r="44" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>1118</v>
+        <v>1144</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>147</v>
@@ -7154,7 +8355,7 @@
         <v>148</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>559</v>
@@ -7169,7 +8370,7 @@
         <v>348</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>1271</v>
+        <v>1295</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
@@ -7184,7 +8385,7 @@
     </row>
     <row r="45" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>1118</v>
+        <v>1144</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>149</v>
@@ -7193,7 +8394,7 @@
         <v>150</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>563</v>
@@ -7208,7 +8409,7 @@
         <v>348</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>1273</v>
+        <v>1297</v>
       </c>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
@@ -7223,7 +8424,7 @@
     </row>
     <row r="46" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>1120</v>
+        <v>1146</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>151</v>
@@ -7232,7 +8433,7 @@
         <v>152</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1274</v>
+        <v>1298</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>567</v>
@@ -7247,10 +8448,10 @@
         <v>337</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>1275</v>
+        <v>1299</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>1276</v>
+        <v>1300</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>1028</v>
@@ -7264,7 +8465,7 @@
     </row>
     <row r="47" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>1120</v>
+        <v>1146</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>153</v>
@@ -7273,7 +8474,7 @@
         <v>154</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1277</v>
+        <v>1301</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>572</v>
@@ -7288,10 +8489,10 @@
         <v>337</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>1278</v>
+        <v>1302</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>1279</v>
+        <v>1303</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>1028</v>
@@ -7305,7 +8506,7 @@
     </row>
     <row r="48" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>1120</v>
+        <v>1146</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>155</v>
@@ -7314,7 +8515,7 @@
         <v>156</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1280</v>
+        <v>1304</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>578</v>
@@ -7329,10 +8530,10 @@
         <v>337</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1281</v>
+        <v>1305</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>1282</v>
+        <v>1306</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>1028</v>
@@ -7346,7 +8547,7 @@
     </row>
     <row r="49" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>1122</v>
+        <v>1148</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>159</v>
@@ -7355,7 +8556,7 @@
         <v>160</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1283</v>
+        <v>1307</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>580</v>
@@ -7370,7 +8571,7 @@
         <v>348</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>1284</v>
+        <v>1308</v>
       </c>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
@@ -7385,7 +8586,7 @@
     </row>
     <row r="50" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>1122</v>
+        <v>1148</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>161</v>
@@ -7394,7 +8595,7 @@
         <v>162</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1285</v>
+        <v>1309</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>584</v>
@@ -7409,10 +8610,10 @@
         <v>337</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>1286</v>
+        <v>1310</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>1287</v>
+        <v>1311</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>1028</v>
@@ -7426,7 +8627,7 @@
     </row>
     <row r="51" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>1122</v>
+        <v>1148</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>163</v>
@@ -7435,7 +8636,7 @@
         <v>164</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1288</v>
+        <v>1312</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>590</v>
@@ -7450,10 +8651,10 @@
         <v>337</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>1289</v>
+        <v>1313</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>1290</v>
+        <v>1314</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>1028</v>
@@ -7467,7 +8668,7 @@
     </row>
     <row r="52" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>1126</v>
+        <v>1152</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>165</v>
@@ -7476,7 +8677,7 @@
         <v>166</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>1291</v>
+        <v>1315</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>596</v>
@@ -7491,10 +8692,10 @@
         <v>337</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>1292</v>
+        <v>1316</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>1293</v>
+        <v>1317</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>1028</v>
@@ -7508,7 +8709,7 @@
     </row>
     <row r="53" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>1126</v>
+        <v>1152</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>167</v>
@@ -7517,7 +8718,7 @@
         <v>168</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>1294</v>
+        <v>1318</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>602</v>
@@ -7532,7 +8733,7 @@
         <v>348</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>1295</v>
+        <v>1319</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
@@ -7547,7 +8748,7 @@
     </row>
     <row r="54" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>1126</v>
+        <v>1152</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>169</v>
@@ -7556,7 +8757,7 @@
         <v>170</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1296</v>
+        <v>1320</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>606</v>
@@ -7571,7 +8772,7 @@
         <v>348</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>1297</v>
+        <v>1321</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
@@ -7586,7 +8787,7 @@
     </row>
     <row r="55" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>1126</v>
+        <v>1152</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>171</v>
@@ -7595,7 +8796,7 @@
         <v>172</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1298</v>
+        <v>1322</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>610</v>
@@ -7610,7 +8811,7 @@
         <v>348</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>1299</v>
+        <v>1323</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
@@ -7625,7 +8826,7 @@
     </row>
     <row r="56" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>1126</v>
+        <v>1152</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>173</v>
@@ -7634,7 +8835,7 @@
         <v>174</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>1300</v>
+        <v>1324</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>614</v>
@@ -7649,7 +8850,7 @@
         <v>348</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>1301</v>
+        <v>1325</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
@@ -7664,7 +8865,7 @@
     </row>
     <row r="57" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>1128</v>
+        <v>1154</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>175</v>
@@ -7673,7 +8874,7 @@
         <v>176</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>1302</v>
+        <v>1326</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>618</v>
@@ -7688,7 +8889,7 @@
         <v>348</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>1303</v>
+        <v>1327</v>
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
@@ -7703,7 +8904,7 @@
     </row>
     <row r="58" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>1128</v>
+        <v>1154</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>177</v>
@@ -7712,7 +8913,7 @@
         <v>178</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>1304</v>
+        <v>1328</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>622</v>
@@ -7727,10 +8928,10 @@
         <v>337</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>1305</v>
+        <v>1329</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>1306</v>
+        <v>1330</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>1028</v>
@@ -7744,7 +8945,7 @@
     </row>
     <row r="59" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>1128</v>
+        <v>1154</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>179</v>
@@ -7753,7 +8954,7 @@
         <v>180</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>1307</v>
+        <v>1331</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>629</v>
@@ -7768,10 +8969,10 @@
         <v>337</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>1308</v>
+        <v>1332</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>1309</v>
+        <v>1333</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>1028</v>
@@ -7785,7 +8986,7 @@
     </row>
     <row r="60" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>1128</v>
+        <v>1154</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>181</v>
@@ -7794,7 +8995,7 @@
         <v>182</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>1310</v>
+        <v>1334</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>636</v>
@@ -7809,7 +9010,7 @@
         <v>348</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>1311</v>
+        <v>1335</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
@@ -7824,7 +9025,7 @@
     </row>
     <row r="61" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>1130</v>
+        <v>1043</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>183</v>
@@ -7833,7 +9034,7 @@
         <v>184</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1312</v>
+        <v>1336</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>640</v>
@@ -7848,10 +9049,10 @@
         <v>337</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>1313</v>
+        <v>1337</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>1314</v>
+        <v>1338</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>1028</v>
@@ -7865,7 +9066,7 @@
     </row>
     <row r="62" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>1130</v>
+        <v>1043</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>185</v>
@@ -7874,7 +9075,7 @@
         <v>186</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>1315</v>
+        <v>1339</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>646</v>
@@ -7889,7 +9090,7 @@
         <v>348</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>1316</v>
+        <v>1340</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
@@ -7904,7 +9105,7 @@
     </row>
     <row r="63" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>1130</v>
+        <v>1043</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>187</v>
@@ -7913,7 +9114,7 @@
         <v>188</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1317</v>
+        <v>1341</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>650</v>
@@ -7928,7 +9129,7 @@
         <v>348</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>1318</v>
+        <v>1342</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
@@ -7943,7 +9144,7 @@
     </row>
     <row r="64" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>1130</v>
+        <v>1043</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>189</v>
@@ -7952,7 +9153,7 @@
         <v>190</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1319</v>
+        <v>1343</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>654</v>
@@ -7967,7 +9168,7 @@
         <v>348</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>1320</v>
+        <v>1344</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
@@ -7982,7 +9183,7 @@
     </row>
     <row r="65" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>1130</v>
+        <v>1043</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>191</v>
@@ -7991,7 +9192,7 @@
         <v>192</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>1321</v>
+        <v>1345</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>658</v>
@@ -8006,7 +9207,7 @@
         <v>348</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>1322</v>
+        <v>1346</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
@@ -8021,7 +9222,7 @@
     </row>
     <row r="66" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>1134</v>
+        <v>1159</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>193</v>
@@ -8030,7 +9231,7 @@
         <v>194</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>1323</v>
+        <v>1347</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>662</v>
@@ -8045,10 +9246,10 @@
         <v>337</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>1324</v>
+        <v>1348</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>1325</v>
+        <v>1349</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>1028</v>
@@ -8062,7 +9263,7 @@
     </row>
     <row r="67" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>1134</v>
+        <v>1159</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>195</v>
@@ -8071,7 +9272,7 @@
         <v>196</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>1326</v>
+        <v>1350</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>667</v>
@@ -8086,10 +9287,10 @@
         <v>337</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>1327</v>
+        <v>1351</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>1328</v>
+        <v>1352</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>1028</v>
@@ -8103,7 +9304,7 @@
     </row>
     <row r="68" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>1134</v>
+        <v>1159</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>197</v>
@@ -8112,7 +9313,7 @@
         <v>198</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>1329</v>
+        <v>1353</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>674</v>
@@ -8127,10 +9328,10 @@
         <v>337</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>1330</v>
+        <v>1354</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>1331</v>
+        <v>1355</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>1028</v>
@@ -8144,7 +9345,7 @@
     </row>
     <row r="69" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>1134</v>
+        <v>1159</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>199</v>
@@ -8153,7 +9354,7 @@
         <v>200</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>1332</v>
+        <v>1356</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>681</v>
@@ -8168,7 +9369,7 @@
         <v>348</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>1333</v>
+        <v>1357</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
@@ -8183,7 +9384,7 @@
     </row>
     <row r="70" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>1134</v>
+        <v>1159</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>201</v>
@@ -8192,7 +9393,7 @@
         <v>202</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>1334</v>
+        <v>1358</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>685</v>
@@ -8207,7 +9408,7 @@
         <v>348</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>1335</v>
+        <v>1359</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
@@ -8222,7 +9423,7 @@
     </row>
     <row r="71" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>1134</v>
+        <v>1159</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>203</v>
@@ -8231,7 +9432,7 @@
         <v>204</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1336</v>
+        <v>1360</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>689</v>
@@ -8246,10 +9447,10 @@
         <v>337</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>1337</v>
+        <v>1361</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>1338</v>
+        <v>1362</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>1028</v>
@@ -8263,7 +9464,7 @@
     </row>
     <row r="72" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>1136</v>
+        <v>1161</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>205</v>
@@ -8272,7 +9473,7 @@
         <v>206</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>1339</v>
+        <v>1363</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>695</v>
@@ -8287,10 +9488,10 @@
         <v>337</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>1340</v>
+        <v>1364</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>1341</v>
+        <v>1365</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>1028</v>
@@ -8304,7 +9505,7 @@
     </row>
     <row r="73" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>1136</v>
+        <v>1161</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>205</v>
@@ -8313,7 +9514,7 @@
         <v>206</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>1339</v>
+        <v>1363</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>702</v>
@@ -8328,10 +9529,10 @@
         <v>337</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>1342</v>
+        <v>1366</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>1341</v>
+        <v>1365</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>1028</v>
@@ -8345,7 +9546,7 @@
     </row>
     <row r="74" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>1136</v>
+        <v>1161</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>207</v>
@@ -8354,7 +9555,7 @@
         <v>208</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>1343</v>
+        <v>1367</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>708</v>
@@ -8369,7 +9570,7 @@
         <v>348</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>1344</v>
+        <v>1368</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
@@ -8384,7 +9585,7 @@
     </row>
     <row r="75" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>1136</v>
+        <v>1161</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>209</v>
@@ -8393,7 +9594,7 @@
         <v>210</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>1345</v>
+        <v>1369</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>712</v>
@@ -8408,10 +9609,10 @@
         <v>337</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>1346</v>
+        <v>1370</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>1347</v>
+        <v>1371</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>1028</v>
@@ -8425,7 +9626,7 @@
     </row>
     <row r="76" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>1136</v>
+        <v>1161</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>209</v>
@@ -8434,7 +9635,7 @@
         <v>210</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>1345</v>
+        <v>1369</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>719</v>
@@ -8449,10 +9650,10 @@
         <v>337</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>1348</v>
+        <v>1372</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>1347</v>
+        <v>1371</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>1028</v>
@@ -8466,7 +9667,7 @@
     </row>
     <row r="77" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>1136</v>
+        <v>1161</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>209</v>
@@ -8475,7 +9676,7 @@
         <v>210</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>1345</v>
+        <v>1369</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>725</v>
@@ -8490,10 +9691,10 @@
         <v>337</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>1349</v>
+        <v>1373</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>1347</v>
+        <v>1371</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>1028</v>
@@ -8507,7 +9708,7 @@
     </row>
     <row r="78" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>1136</v>
+        <v>1161</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>211</v>
@@ -8516,7 +9717,7 @@
         <v>212</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>1350</v>
+        <v>1374</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>731</v>
@@ -8531,10 +9732,10 @@
         <v>337</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>1351</v>
+        <v>1375</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>1352</v>
+        <v>1376</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>1028</v>
@@ -8548,7 +9749,7 @@
     </row>
     <row r="79" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>1136</v>
+        <v>1161</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>213</v>
@@ -8557,7 +9758,7 @@
         <v>214</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>1353</v>
+        <v>1377</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>738</v>
@@ -8572,7 +9773,7 @@
         <v>348</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>1354</v>
+        <v>1378</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
@@ -8587,7 +9788,7 @@
     </row>
     <row r="80" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>1136</v>
+        <v>1161</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>215</v>
@@ -8596,7 +9797,7 @@
         <v>216</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>1355</v>
+        <v>1379</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>742</v>
@@ -8611,7 +9812,7 @@
         <v>348</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>1356</v>
+        <v>1380</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
@@ -8626,7 +9827,7 @@
     </row>
     <row r="81" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>1138</v>
+        <v>1050</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>217</v>
@@ -8635,7 +9836,7 @@
         <v>218</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>1357</v>
+        <v>1381</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>746</v>
@@ -8650,10 +9851,10 @@
         <v>337</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>1358</v>
+        <v>1382</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>1359</v>
+        <v>1383</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>1028</v>
@@ -8667,7 +9868,7 @@
     </row>
     <row r="82" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>1138</v>
+        <v>1050</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>219</v>
@@ -8676,7 +9877,7 @@
         <v>220</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>1360</v>
+        <v>1384</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>752</v>
@@ -8691,10 +9892,10 @@
         <v>337</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>1361</v>
+        <v>1385</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>1362</v>
+        <v>1386</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>1028</v>
@@ -8708,7 +9909,7 @@
     </row>
     <row r="83" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>1138</v>
+        <v>1050</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>221</v>
@@ -8717,7 +9918,7 @@
         <v>222</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>1363</v>
+        <v>1387</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>758</v>
@@ -8732,10 +9933,10 @@
         <v>337</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>1364</v>
+        <v>1388</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>1365</v>
+        <v>1389</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>1028</v>
@@ -8749,7 +9950,7 @@
     </row>
     <row r="84" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>1138</v>
+        <v>1050</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>223</v>
@@ -8758,7 +9959,7 @@
         <v>224</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>1366</v>
+        <v>1390</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>764</v>
@@ -8773,7 +9974,7 @@
         <v>348</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>1367</v>
+        <v>1391</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
@@ -8788,7 +9989,7 @@
     </row>
     <row r="85" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>1138</v>
+        <v>1050</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>225</v>
@@ -8797,7 +9998,7 @@
         <v>226</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>1368</v>
+        <v>1392</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>768</v>
@@ -8812,7 +10013,7 @@
         <v>348</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>1369</v>
+        <v>1393</v>
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
@@ -8827,7 +10028,7 @@
     </row>
     <row r="86" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>1138</v>
+        <v>1050</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>227</v>
@@ -8836,7 +10037,7 @@
         <v>228</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>1370</v>
+        <v>1394</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>772</v>
@@ -8851,7 +10052,7 @@
         <v>348</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>1371</v>
+        <v>1395</v>
       </c>
       <c r="J86" s="2"/>
       <c r="K86" s="2" t="s">
@@ -8866,7 +10067,7 @@
     </row>
     <row r="87" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>1140</v>
+        <v>1164</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>229</v>
@@ -8875,7 +10076,7 @@
         <v>230</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>1372</v>
+        <v>1396</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>776</v>
@@ -8890,10 +10091,10 @@
         <v>337</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>1373</v>
+        <v>1397</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>1374</v>
+        <v>1398</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>1028</v>
@@ -8907,7 +10108,7 @@
     </row>
     <row r="88" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>1140</v>
+        <v>1164</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>231</v>
@@ -8916,7 +10117,7 @@
         <v>232</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>1375</v>
+        <v>1399</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>782</v>
@@ -8931,10 +10132,10 @@
         <v>337</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>1376</v>
+        <v>1400</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>1377</v>
+        <v>1401</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>1028</v>
@@ -8948,7 +10149,7 @@
     </row>
     <row r="89" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>1140</v>
+        <v>1164</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>233</v>
@@ -8957,7 +10158,7 @@
         <v>234</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>1378</v>
+        <v>1402</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>787</v>
@@ -8972,10 +10173,10 @@
         <v>337</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>1379</v>
+        <v>1403</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>1380</v>
+        <v>1404</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>1028</v>
@@ -8989,7 +10190,7 @@
     </row>
     <row r="90" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>1144</v>
+        <v>1168</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>235</v>
@@ -8998,7 +10199,7 @@
         <v>236</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>1381</v>
+        <v>1405</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>793</v>
@@ -9013,10 +10214,10 @@
         <v>337</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>1382</v>
+        <v>1406</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>1383</v>
+        <v>1407</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>1028</v>
@@ -9030,7 +10231,7 @@
     </row>
     <row r="91" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>1144</v>
+        <v>1168</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>237</v>
@@ -9039,7 +10240,7 @@
         <v>238</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>1384</v>
+        <v>1408</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>799</v>
@@ -9054,10 +10255,10 @@
         <v>337</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>1385</v>
+        <v>1409</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>1386</v>
+        <v>1410</v>
       </c>
       <c r="K91" s="2" t="s">
         <v>1028</v>
@@ -9071,7 +10272,7 @@
     </row>
     <row r="92" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>1144</v>
+        <v>1168</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>239</v>
@@ -9080,7 +10281,7 @@
         <v>240</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>1387</v>
+        <v>1411</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>801</v>
@@ -9095,7 +10296,7 @@
         <v>348</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>1388</v>
+        <v>1412</v>
       </c>
       <c r="J92" s="2"/>
       <c r="K92" s="2" t="s">
@@ -9110,7 +10311,7 @@
     </row>
     <row r="93" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>1144</v>
+        <v>1168</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>241</v>
@@ -9119,7 +10320,7 @@
         <v>242</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>1389</v>
+        <v>1413</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>805</v>
@@ -9134,7 +10335,7 @@
         <v>348</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>1390</v>
+        <v>1414</v>
       </c>
       <c r="J93" s="2"/>
       <c r="K93" s="2" t="s">
@@ -9149,7 +10350,7 @@
     </row>
     <row r="94" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>1144</v>
+        <v>1168</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>243</v>
@@ -9158,7 +10359,7 @@
         <v>244</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>1391</v>
+        <v>1415</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>809</v>
@@ -9173,10 +10374,10 @@
         <v>337</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>1392</v>
+        <v>1416</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>1393</v>
+        <v>1417</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>1028</v>
@@ -9190,7 +10391,7 @@
     </row>
     <row r="95" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>1146</v>
+        <v>1170</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>245</v>
@@ -9199,7 +10400,7 @@
         <v>246</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>1394</v>
+        <v>1418</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>811</v>
@@ -9214,7 +10415,7 @@
         <v>348</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>1395</v>
+        <v>1419</v>
       </c>
       <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
@@ -9229,7 +10430,7 @@
     </row>
     <row r="96" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>1146</v>
+        <v>1170</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>247</v>
@@ -9238,7 +10439,7 @@
         <v>248</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>1396</v>
+        <v>1420</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>815</v>
@@ -9253,10 +10454,10 @@
         <v>337</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>1397</v>
+        <v>1421</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>1398</v>
+        <v>1422</v>
       </c>
       <c r="K96" s="2" t="s">
         <v>1028</v>
@@ -9270,7 +10471,7 @@
     </row>
     <row r="97" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>1146</v>
+        <v>1170</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>249</v>
@@ -9279,7 +10480,7 @@
         <v>250</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>1399</v>
+        <v>1423</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>822</v>
@@ -9294,7 +10495,7 @@
         <v>348</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>1400</v>
+        <v>1424</v>
       </c>
       <c r="J97" s="2"/>
       <c r="K97" s="2" t="s">
@@ -9309,7 +10510,7 @@
     </row>
     <row r="98" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>1146</v>
+        <v>1170</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>251</v>
@@ -9318,7 +10519,7 @@
         <v>252</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>1401</v>
+        <v>1425</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>826</v>
@@ -9333,7 +10534,7 @@
         <v>348</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>1402</v>
+        <v>1426</v>
       </c>
       <c r="J98" s="2"/>
       <c r="K98" s="2" t="s">
@@ -9348,7 +10549,7 @@
     </row>
     <row r="99" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>1146</v>
+        <v>1170</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>253</v>
@@ -9357,7 +10558,7 @@
         <v>254</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>1403</v>
+        <v>1427</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>830</v>
@@ -9372,7 +10573,7 @@
         <v>348</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>1404</v>
+        <v>1428</v>
       </c>
       <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
@@ -9387,7 +10588,7 @@
     </row>
     <row r="100" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>1148</v>
+        <v>1172</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>255</v>
@@ -9396,7 +10597,7 @@
         <v>256</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>1405</v>
+        <v>1429</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>834</v>
@@ -9411,10 +10612,10 @@
         <v>337</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>1406</v>
+        <v>1430</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>1407</v>
+        <v>1431</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>1028</v>
@@ -9428,7 +10629,7 @@
     </row>
     <row r="101" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>1148</v>
+        <v>1172</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>257</v>
@@ -9437,7 +10638,7 @@
         <v>258</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>1408</v>
+        <v>1432</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>840</v>
@@ -9452,7 +10653,7 @@
         <v>348</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>1409</v>
+        <v>1433</v>
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2" t="s">
@@ -9467,7 +10668,7 @@
     </row>
     <row r="102" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>1148</v>
+        <v>1172</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>259</v>
@@ -9476,7 +10677,7 @@
         <v>260</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>1410</v>
+        <v>1434</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>844</v>
@@ -9491,7 +10692,7 @@
         <v>348</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>1411</v>
+        <v>1435</v>
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="2" t="s">
@@ -9506,7 +10707,7 @@
     </row>
     <row r="103" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>1152</v>
+        <v>1176</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>261</v>
@@ -9515,7 +10716,7 @@
         <v>262</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>1412</v>
+        <v>1436</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>848</v>
@@ -9530,7 +10731,7 @@
         <v>348</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>1413</v>
+        <v>1437</v>
       </c>
       <c r="J103" s="2"/>
       <c r="K103" s="2" t="s">
@@ -9545,7 +10746,7 @@
     </row>
     <row r="104" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>1152</v>
+        <v>1176</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>263</v>
@@ -9554,7 +10755,7 @@
         <v>264</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>1414</v>
+        <v>1438</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>852</v>
@@ -9569,7 +10770,7 @@
         <v>348</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>1415</v>
+        <v>1439</v>
       </c>
       <c r="J104" s="2"/>
       <c r="K104" s="2" t="s">
@@ -9584,7 +10785,7 @@
     </row>
     <row r="105" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>1152</v>
+        <v>1176</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>265</v>
@@ -9593,7 +10794,7 @@
         <v>266</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>1416</v>
+        <v>1440</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>856</v>
@@ -9608,7 +10809,7 @@
         <v>348</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>1417</v>
+        <v>1441</v>
       </c>
       <c r="J105" s="2"/>
       <c r="K105" s="2" t="s">
@@ -9623,7 +10824,7 @@
     </row>
     <row r="106" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>1152</v>
+        <v>1176</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>267</v>
@@ -9632,7 +10833,7 @@
         <v>268</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>1418</v>
+        <v>1442</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>860</v>
@@ -9647,10 +10848,10 @@
         <v>337</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>1419</v>
+        <v>1443</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>1420</v>
+        <v>1444</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>1028</v>
@@ -9664,7 +10865,7 @@
     </row>
     <row r="107" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>1152</v>
+        <v>1176</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>269</v>
@@ -9673,7 +10874,7 @@
         <v>270</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>1421</v>
+        <v>1445</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>862</v>
@@ -9688,7 +10889,7 @@
         <v>348</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>1422</v>
+        <v>1446</v>
       </c>
       <c r="J107" s="2"/>
       <c r="K107" s="2" t="s">
@@ -9703,7 +10904,7 @@
     </row>
     <row r="108" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>1154</v>
+        <v>1178</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>271</v>
@@ -9712,7 +10913,7 @@
         <v>272</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1423</v>
+        <v>1447</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>866</v>
@@ -9727,10 +10928,10 @@
         <v>337</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>1424</v>
+        <v>1448</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>1425</v>
+        <v>1449</v>
       </c>
       <c r="K108" s="2" t="s">
         <v>1028</v>
@@ -9744,7 +10945,7 @@
     </row>
     <row r="109" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>1154</v>
+        <v>1178</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>273</v>
@@ -9753,7 +10954,7 @@
         <v>274</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>1426</v>
+        <v>1450</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>872</v>
@@ -9768,7 +10969,7 @@
         <v>348</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>1427</v>
+        <v>1451</v>
       </c>
       <c r="J109" s="2"/>
       <c r="K109" s="2" t="s">
@@ -9783,7 +10984,7 @@
     </row>
     <row r="110" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>1154</v>
+        <v>1178</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>275</v>
@@ -9792,7 +10993,7 @@
         <v>276</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>1428</v>
+        <v>1452</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>876</v>
@@ -9807,7 +11008,7 @@
         <v>348</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>1429</v>
+        <v>1453</v>
       </c>
       <c r="J110" s="2"/>
       <c r="K110" s="2" t="s">
@@ -9822,7 +11023,7 @@
     </row>
     <row r="111" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>1154</v>
+        <v>1178</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>277</v>
@@ -9831,7 +11032,7 @@
         <v>278</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>1430</v>
+        <v>1454</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>880</v>
@@ -9846,7 +11047,7 @@
         <v>348</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>1431</v>
+        <v>1455</v>
       </c>
       <c r="J111" s="2"/>
       <c r="K111" s="2" t="s">
@@ -9861,7 +11062,7 @@
     </row>
     <row r="112" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>1154</v>
+        <v>1178</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>279</v>
@@ -9870,7 +11071,7 @@
         <v>280</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>1432</v>
+        <v>1456</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>884</v>
@@ -9885,7 +11086,7 @@
         <v>348</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>1433</v>
+        <v>1457</v>
       </c>
       <c r="J112" s="2"/>
       <c r="K112" s="2" t="s">
@@ -9900,7 +11101,7 @@
     </row>
     <row r="113" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>1154</v>
+        <v>1178</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>281</v>
@@ -9909,7 +11110,7 @@
         <v>282</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>1434</v>
+        <v>1458</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>888</v>
@@ -9924,7 +11125,7 @@
         <v>348</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>1435</v>
+        <v>1459</v>
       </c>
       <c r="J113" s="2"/>
       <c r="K113" s="2" t="s">
@@ -9939,7 +11140,7 @@
     </row>
     <row r="114" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>1156</v>
+        <v>1180</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>283</v>
@@ -9948,7 +11149,7 @@
         <v>284</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>1436</v>
+        <v>1460</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>892</v>
@@ -9963,7 +11164,7 @@
         <v>348</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>1437</v>
+        <v>1461</v>
       </c>
       <c r="J114" s="2"/>
       <c r="K114" s="2" t="s">
@@ -9978,7 +11179,7 @@
     </row>
     <row r="115" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>1156</v>
+        <v>1180</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>285</v>
@@ -9987,7 +11188,7 @@
         <v>286</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>1438</v>
+        <v>1462</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>896</v>
@@ -10002,7 +11203,7 @@
         <v>348</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>1439</v>
+        <v>1463</v>
       </c>
       <c r="J115" s="2"/>
       <c r="K115" s="2" t="s">
@@ -10017,7 +11218,7 @@
     </row>
     <row r="116" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>1156</v>
+        <v>1180</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>287</v>
@@ -10026,7 +11227,7 @@
         <v>288</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>1440</v>
+        <v>1464</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>900</v>
@@ -10041,7 +11242,7 @@
         <v>348</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>1441</v>
+        <v>1465</v>
       </c>
       <c r="J116" s="2"/>
       <c r="K116" s="2" t="s">
@@ -10056,7 +11257,7 @@
     </row>
     <row r="117" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>1156</v>
+        <v>1180</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>289</v>
@@ -10065,7 +11266,7 @@
         <v>290</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>1442</v>
+        <v>1466</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>904</v>
@@ -10080,10 +11281,10 @@
         <v>337</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>1443</v>
+        <v>1467</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>1444</v>
+        <v>1468</v>
       </c>
       <c r="K117" s="2" t="s">
         <v>1028</v>
@@ -10097,7 +11298,7 @@
     </row>
     <row r="118" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>1158</v>
+        <v>1182</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>291</v>
@@ -10106,7 +11307,7 @@
         <v>292</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>1445</v>
+        <v>1469</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>909</v>
@@ -10121,7 +11322,7 @@
         <v>348</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>1446</v>
+        <v>1470</v>
       </c>
       <c r="J118" s="2"/>
       <c r="K118" s="2" t="s">
@@ -10136,7 +11337,7 @@
     </row>
     <row r="119" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>1158</v>
+        <v>1182</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>293</v>
@@ -10145,7 +11346,7 @@
         <v>294</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1447</v>
+        <v>1471</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>913</v>
@@ -10160,7 +11361,7 @@
         <v>348</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>1448</v>
+        <v>1472</v>
       </c>
       <c r="J119" s="2"/>
       <c r="K119" s="2" t="s">
@@ -10175,7 +11376,7 @@
     </row>
     <row r="120" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>1158</v>
+        <v>1182</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>295</v>
@@ -10184,7 +11385,7 @@
         <v>296</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>1449</v>
+        <v>1473</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>917</v>
@@ -10199,7 +11400,7 @@
         <v>348</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>1450</v>
+        <v>1474</v>
       </c>
       <c r="J120" s="2"/>
       <c r="K120" s="2" t="s">
@@ -10214,7 +11415,7 @@
     </row>
     <row r="121" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>1158</v>
+        <v>1182</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>297</v>
@@ -10223,7 +11424,7 @@
         <v>298</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>1451</v>
+        <v>1475</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>921</v>
@@ -10238,7 +11439,7 @@
         <v>348</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>1452</v>
+        <v>1476</v>
       </c>
       <c r="J121" s="2"/>
       <c r="K121" s="2" t="s">
@@ -10253,7 +11454,7 @@
     </row>
     <row r="122" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>1453</v>
+        <v>1152</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>299</v>
@@ -10262,7 +11463,7 @@
         <v>300</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>1454</v>
+        <v>1477</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>925</v>
@@ -10277,10 +11478,10 @@
         <v>337</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>1455</v>
+        <v>1478</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>1456</v>
+        <v>1479</v>
       </c>
       <c r="K122" s="2" t="s">
         <v>1028</v>
@@ -10294,7 +11495,7 @@
     </row>
     <row r="123" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>1453</v>
+        <v>1043</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>301</v>
@@ -10303,7 +11504,7 @@
         <v>302</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>1457</v>
+        <v>1480</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>931</v>
@@ -10318,10 +11519,10 @@
         <v>337</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>1458</v>
+        <v>1481</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>1459</v>
+        <v>1482</v>
       </c>
       <c r="K123" s="2" t="s">
         <v>1028</v>
@@ -10335,7 +11536,7 @@
     </row>
     <row r="124" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>1453</v>
+        <v>1043</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>301</v>
@@ -10344,7 +11545,7 @@
         <v>302</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1457</v>
+        <v>1480</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>938</v>
@@ -10359,16 +11560,16 @@
         <v>337</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>1460</v>
+        <v>1483</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>1459</v>
+        <v>1482</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="L124" s="2" t="s">
-        <v>339</v>
+        <v>1040</v>
       </c>
       <c r="M124" s="2" t="s">
         <v>339</v>
@@ -10376,7 +11577,7 @@
     </row>
     <row r="125" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>1461</v>
+        <v>1172</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>303</v>
@@ -10385,7 +11586,7 @@
         <v>304</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>1462</v>
+        <v>1484</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>944</v>
@@ -10400,10 +11601,10 @@
         <v>337</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>1463</v>
+        <v>1485</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>1464</v>
+        <v>1486</v>
       </c>
       <c r="K125" s="2" t="s">
         <v>1028</v>
@@ -10417,7 +11618,7 @@
     </row>
     <row r="126" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>1465</v>
+        <v>1050</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>305</v>
@@ -10426,7 +11627,7 @@
         <v>306</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>1466</v>
+        <v>1487</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>950</v>
@@ -10441,10 +11642,10 @@
         <v>337</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>1467</v>
+        <v>1488</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>1468</v>
+        <v>1489</v>
       </c>
       <c r="K126" s="2" t="s">
         <v>1028</v>
@@ -10458,7 +11659,7 @@
     </row>
     <row r="127" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>1465</v>
+        <v>1050</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>305</v>
@@ -10467,7 +11668,7 @@
         <v>306</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>1466</v>
+        <v>1487</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>956</v>
@@ -10482,16 +11683,16 @@
         <v>337</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>1469</v>
+        <v>1490</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>1468</v>
+        <v>1489</v>
       </c>
       <c r="K127" s="2" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="L127" s="2" t="s">
-        <v>339</v>
+        <v>1048</v>
       </c>
       <c r="M127" s="2" t="s">
         <v>339</v>
@@ -10499,7 +11700,7 @@
     </row>
     <row r="128" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>1465</v>
+        <v>1050</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>305</v>
@@ -10508,7 +11709,7 @@
         <v>306</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>1466</v>
+        <v>1487</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>960</v>
@@ -10523,10 +11724,10 @@
         <v>337</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>1470</v>
+        <v>1491</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>1468</v>
+        <v>1489</v>
       </c>
       <c r="K128" s="2" t="s">
         <v>1028</v>
@@ -10540,7 +11741,7 @@
     </row>
     <row r="129" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>1471</v>
+        <v>1057</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>307</v>
@@ -10549,7 +11750,7 @@
         <v>308</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>1472</v>
+        <v>1492</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>965</v>
@@ -10564,10 +11765,10 @@
         <v>337</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>1473</v>
+        <v>1493</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>1474</v>
+        <v>1494</v>
       </c>
       <c r="K129" s="2" t="s">
         <v>1028</v>
@@ -10581,7 +11782,7 @@
     </row>
     <row r="130" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>1471</v>
+        <v>1057</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>307</v>
@@ -10590,7 +11791,7 @@
         <v>308</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>1472</v>
+        <v>1492</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>972</v>
@@ -10605,10 +11806,10 @@
         <v>337</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>1475</v>
+        <v>1495</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>1474</v>
+        <v>1494</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>1028</v>
@@ -10622,7 +11823,7 @@
     </row>
     <row r="131" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>1471</v>
+        <v>1057</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>307</v>
@@ -10631,7 +11832,7 @@
         <v>308</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>1472</v>
+        <v>1492</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>978</v>
@@ -10646,10 +11847,10 @@
         <v>337</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>1476</v>
+        <v>1496</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>1474</v>
+        <v>1494</v>
       </c>
       <c r="K131" s="2" t="s">
         <v>1028</v>
@@ -10663,7 +11864,7 @@
     </row>
     <row r="132" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>1471</v>
+        <v>1057</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>307</v>
@@ -10672,7 +11873,7 @@
         <v>308</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>1472</v>
+        <v>1492</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>983</v>
@@ -10687,10 +11888,10 @@
         <v>337</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>1477</v>
+        <v>1497</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>1474</v>
+        <v>1494</v>
       </c>
       <c r="K132" s="2" t="s">
         <v>1028</v>
@@ -10704,7 +11905,7 @@
     </row>
     <row r="133" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>1471</v>
+        <v>1057</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>309</v>
@@ -10713,7 +11914,7 @@
         <v>310</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1478</v>
+        <v>1498</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>988</v>
@@ -10728,10 +11929,10 @@
         <v>337</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>1479</v>
+        <v>1499</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>1480</v>
+        <v>1500</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>1028</v>
@@ -10745,7 +11946,7 @@
     </row>
     <row r="134" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>1471</v>
+        <v>1057</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>309</v>
@@ -10754,7 +11955,7 @@
         <v>310</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>1478</v>
+        <v>1498</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>994</v>
@@ -10769,10 +11970,10 @@
         <v>337</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>1481</v>
+        <v>1501</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>1480</v>
+        <v>1500</v>
       </c>
       <c r="K134" s="2" t="s">
         <v>1028</v>
@@ -10786,7 +11987,7 @@
     </row>
     <row r="135" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>1471</v>
+        <v>1057</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>309</v>
@@ -10795,7 +11996,7 @@
         <v>310</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>1478</v>
+        <v>1498</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>1000</v>
@@ -10810,10 +12011,10 @@
         <v>337</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>1482</v>
+        <v>1502</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>1480</v>
+        <v>1500</v>
       </c>
       <c r="K135" s="2" t="s">
         <v>1028</v>
@@ -10827,7 +12028,7 @@
     </row>
     <row r="136" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>1471</v>
+        <v>1057</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>309</v>
@@ -10836,7 +12037,7 @@
         <v>310</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>1478</v>
+        <v>1498</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>1006</v>
@@ -10851,16 +12052,16 @@
         <v>337</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>1483</v>
+        <v>1503</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>1480</v>
+        <v>1500</v>
       </c>
       <c r="K136" s="2" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="L136" s="2" t="s">
-        <v>339</v>
+        <v>1055</v>
       </c>
       <c r="M136" s="2" t="s">
         <v>339</v>
@@ -10868,7 +12069,7 @@
     </row>
     <row r="137" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>1471</v>
+        <v>1057</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>311</v>
@@ -10877,7 +12078,7 @@
         <v>312</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>1484</v>
+        <v>1504</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>1012</v>
@@ -10892,10 +12093,10 @@
         <v>337</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>1485</v>
+        <v>1505</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>1486</v>
+        <v>1506</v>
       </c>
       <c r="K137" s="2" t="s">
         <v>1028</v>
@@ -10909,7 +12110,7 @@
     </row>
     <row r="138" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>1471</v>
+        <v>1057</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>311</v>
@@ -10918,7 +12119,7 @@
         <v>312</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>1484</v>
+        <v>1504</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>1018</v>
@@ -10933,10 +12134,10 @@
         <v>337</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>1487</v>
+        <v>1507</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>1486</v>
+        <v>1506</v>
       </c>
       <c r="K138" s="2" t="s">
         <v>1028</v>
@@ -10954,7 +12155,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -10968,36 +12169,36 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1488</v>
+        <v>1508</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1489</v>
+        <v>1509</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1490</v>
+        <v>1510</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1491</v>
+        <v>1511</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1492</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1493</v>
+        <v>1513</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1494</v>
+        <v>1514</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1495</v>
+        <v>1515</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1496</v>
+        <v>1516</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1497</v>
+        <v>1517</v>
       </c>
     </row>
   </sheetData>
@@ -11006,7 +12207,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -11020,189 +12221,189 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1498</v>
+        <v>1518</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>314</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1046</v>
+        <v>1071</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1499</v>
+        <v>1519</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1500</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1501</v>
+        <v>1521</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1502</v>
+        <v>1522</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1503</v>
+        <v>1523</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1504</v>
+        <v>1524</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1505</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1506</v>
+        <v>1526</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1507</v>
+        <v>1527</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1508</v>
+        <v>1528</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1509</v>
+        <v>1529</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1510</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1511</v>
+        <v>1531</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1512</v>
+        <v>1532</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1513</v>
+        <v>1533</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1514</v>
+        <v>1534</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1515</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1516</v>
+        <v>1536</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1517</v>
+        <v>1537</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1518</v>
+        <v>1538</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1519</v>
+        <v>1539</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1520</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1521</v>
+        <v>1541</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1522</v>
+        <v>1542</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1523</v>
+        <v>1543</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1524</v>
+        <v>1544</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1525</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1526</v>
+        <v>1546</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1527</v>
+        <v>1547</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1528</v>
+        <v>1548</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1529</v>
+        <v>1549</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1530</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1531</v>
+        <v>1551</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1532</v>
+        <v>1552</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1533</v>
+        <v>1553</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1534</v>
+        <v>1554</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1535</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1536</v>
+        <v>1556</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1537</v>
+        <v>1557</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1538</v>
+        <v>1558</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1539</v>
+        <v>1559</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1540</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1541</v>
+        <v>1561</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1542</v>
+        <v>1562</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1543</v>
+        <v>1563</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1544</v>
+        <v>1564</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1545</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1546</v>
+        <v>1566</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1547</v>
+        <v>1567</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1548</v>
+        <v>1568</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1549</v>
+        <v>1569</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1550</v>
+        <v>1570</v>
       </c>
     </row>
   </sheetData>
@@ -11211,7 +12412,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -11225,186 +12426,186 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1551</v>
+        <v>1571</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1552</v>
+        <v>1572</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1553</v>
+        <v>1573</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1554</v>
+        <v>1574</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1555</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1556</v>
+        <v>1576</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1557</v>
+        <v>1577</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1558</v>
+        <v>1578</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1559</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>1526</v>
+        <v>1546</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1558</v>
+        <v>1578</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1560</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1561</v>
+        <v>1581</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1546</v>
+        <v>1566</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1558</v>
+        <v>1578</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1562</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1563</v>
+        <v>1583</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1564</v>
+        <v>1584</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1558</v>
+        <v>1578</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1565</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1566</v>
+        <v>1586</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1567</v>
+        <v>1587</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1558</v>
+        <v>1578</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1568</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1569</v>
+        <v>1589</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1570</v>
+        <v>1590</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1558</v>
+        <v>1578</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1571</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1572</v>
+        <v>1592</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1573</v>
+        <v>1593</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1558</v>
+        <v>1578</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1574</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1575</v>
+        <v>1595</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1576</v>
+        <v>1596</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1558</v>
+        <v>1578</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1577</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>1578</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>1579</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1558</v>
-      </c>
       <c r="D10" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1580</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1581</v>
+        <v>1601</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1582</v>
+        <v>1602</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1558</v>
+        <v>1578</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1583</v>
+        <v>1603</v>
       </c>
     </row>
   </sheetData>
@@ -20402,7 +21603,7 @@
         <v>1028</v>
       </c>
       <c r="E2" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -20520,7 +21721,7 @@
         <v>1028</v>
       </c>
       <c r="E8" s="2">
-        <v>243</v>
+        <v>205</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -20538,7 +21739,7 @@
         <v>1028</v>
       </c>
       <c r="E9" s="2">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -20556,7 +21757,7 @@
         <v>1028</v>
       </c>
       <c r="E10" s="2">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -20574,7 +21775,7 @@
         <v>1028</v>
       </c>
       <c r="E11" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -20592,7 +21793,7 @@
         <v>1028</v>
       </c>
       <c r="E12" s="2">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -20610,7 +21811,7 @@
         <v>1028</v>
       </c>
       <c r="E13" s="2">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -20688,7 +21889,7 @@
         <v>1028</v>
       </c>
       <c r="E17" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -20706,7 +21907,7 @@
         <v>1028</v>
       </c>
       <c r="E18" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -20784,7 +21985,7 @@
         <v>1028</v>
       </c>
       <c r="E22" s="2">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="F22" s="2"/>
     </row>
@@ -20822,7 +22023,7 @@
         <v>1028</v>
       </c>
       <c r="E24" s="2">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -20858,7 +22059,7 @@
         <v>1028</v>
       </c>
       <c r="E26" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -20876,7 +22077,7 @@
         <v>1028</v>
       </c>
       <c r="E27" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -20894,7 +22095,7 @@
         <v>1028</v>
       </c>
       <c r="E28" s="2">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -20912,7 +22113,7 @@
         <v>1028</v>
       </c>
       <c r="E29" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -20948,7 +22149,7 @@
         <v>1028</v>
       </c>
       <c r="E31" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -20966,7 +22167,7 @@
         <v>1028</v>
       </c>
       <c r="E32" s="2">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F32" s="2"/>
     </row>
@@ -21004,7 +22205,7 @@
         <v>1028</v>
       </c>
       <c r="E34" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -21022,7 +22223,7 @@
         <v>1028</v>
       </c>
       <c r="E35" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F35" s="2"/>
     </row>
@@ -21080,7 +22281,7 @@
         <v>1028</v>
       </c>
       <c r="E38" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F38" s="2"/>
     </row>
@@ -21118,7 +22319,7 @@
         <v>1028</v>
       </c>
       <c r="E40" s="2">
-        <v>196</v>
+        <v>139</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -21136,7 +22337,7 @@
         <v>1028</v>
       </c>
       <c r="E41" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F41" s="2"/>
     </row>
@@ -21252,7 +22453,7 @@
         <v>1028</v>
       </c>
       <c r="E47" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -21308,7 +22509,7 @@
         <v>1028</v>
       </c>
       <c r="E50" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -21326,7 +22527,7 @@
         <v>1028</v>
       </c>
       <c r="E51" s="2">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -21462,7 +22663,7 @@
         <v>1028</v>
       </c>
       <c r="E58" s="2">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -21480,7 +22681,7 @@
         <v>1028</v>
       </c>
       <c r="E59" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F59" s="2"/>
     </row>
@@ -21518,7 +22719,7 @@
         <v>1028</v>
       </c>
       <c r="E61" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F61" s="2"/>
     </row>
@@ -21616,7 +22817,7 @@
         <v>1028</v>
       </c>
       <c r="E66" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -21634,7 +22835,7 @@
         <v>1028</v>
       </c>
       <c r="E67" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -21710,7 +22911,7 @@
         <v>1028</v>
       </c>
       <c r="E71" s="2">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -21728,7 +22929,7 @@
         <v>1028</v>
       </c>
       <c r="E72" s="2">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -21746,7 +22947,7 @@
         <v>1028</v>
       </c>
       <c r="E73" s="2">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="F73" s="2"/>
     </row>
@@ -21784,7 +22985,7 @@
         <v>1028</v>
       </c>
       <c r="E75" s="2">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -21802,7 +23003,7 @@
         <v>1028</v>
       </c>
       <c r="E76" s="2">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -21820,7 +23021,7 @@
         <v>1028</v>
       </c>
       <c r="E77" s="2">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -21838,7 +23039,7 @@
         <v>1028</v>
       </c>
       <c r="E78" s="2">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="F78" s="2"/>
     </row>
@@ -21896,7 +23097,7 @@
         <v>1028</v>
       </c>
       <c r="E81" s="2">
-        <v>106</v>
+        <v>41</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -21914,7 +23115,7 @@
         <v>1028</v>
       </c>
       <c r="E82" s="2">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -21932,7 +23133,7 @@
         <v>1028</v>
       </c>
       <c r="E83" s="2">
-        <v>164</v>
+        <v>58</v>
       </c>
       <c r="F83" s="2"/>
     </row>
@@ -22010,7 +23211,7 @@
         <v>1028</v>
       </c>
       <c r="E87" s="2">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -22028,7 +23229,7 @@
         <v>1028</v>
       </c>
       <c r="E88" s="2">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -22046,7 +23247,7 @@
         <v>1028</v>
       </c>
       <c r="E89" s="2">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -22064,7 +23265,7 @@
         <v>1028</v>
       </c>
       <c r="E90" s="2">
-        <v>134</v>
+        <v>42</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -22082,7 +23283,7 @@
         <v>1028</v>
       </c>
       <c r="E91" s="2">
-        <v>158</v>
+        <v>38</v>
       </c>
       <c r="F91" s="2"/>
     </row>
@@ -22140,7 +23341,7 @@
         <v>1028</v>
       </c>
       <c r="E94" s="2">
-        <v>182</v>
+        <v>44</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -22178,7 +23379,7 @@
         <v>1028</v>
       </c>
       <c r="E96" s="2">
-        <v>215</v>
+        <v>109</v>
       </c>
       <c r="F96" s="2"/>
     </row>
@@ -22256,7 +23457,7 @@
         <v>1028</v>
       </c>
       <c r="E100" s="2">
-        <v>112</v>
+        <v>53</v>
       </c>
       <c r="F100" s="2"/>
     </row>
@@ -22374,7 +23575,7 @@
         <v>1028</v>
       </c>
       <c r="E106" s="2">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -22412,7 +23613,7 @@
         <v>1028</v>
       </c>
       <c r="E108" s="2">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="F108" s="2"/>
     </row>
@@ -22590,7 +23791,7 @@
         <v>1028</v>
       </c>
       <c r="E117" s="2">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -22688,7 +23889,7 @@
         <v>1028</v>
       </c>
       <c r="E122" s="2">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -22706,7 +23907,7 @@
         <v>1028</v>
       </c>
       <c r="E123" s="2">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -22721,10 +23922,10 @@
         <v>939</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="E124" s="2">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -22742,7 +23943,7 @@
         <v>1028</v>
       </c>
       <c r="E125" s="2">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -22760,7 +23961,7 @@
         <v>1028</v>
       </c>
       <c r="E126" s="2">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -22775,10 +23976,10 @@
         <v>957</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="E127" s="2">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -22796,7 +23997,7 @@
         <v>1028</v>
       </c>
       <c r="E128" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -22814,7 +24015,7 @@
         <v>1028</v>
       </c>
       <c r="E129" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -22832,7 +24033,7 @@
         <v>1028</v>
       </c>
       <c r="E130" s="2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -22850,7 +24051,7 @@
         <v>1028</v>
       </c>
       <c r="E131" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -22868,7 +24069,7 @@
         <v>1028</v>
       </c>
       <c r="E132" s="2">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -22886,7 +24087,7 @@
         <v>1028</v>
       </c>
       <c r="E133" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F133" s="2"/>
     </row>
@@ -22904,7 +24105,7 @@
         <v>1028</v>
       </c>
       <c r="E134" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F134" s="2"/>
     </row>
@@ -22922,7 +24123,7 @@
         <v>1028</v>
       </c>
       <c r="E135" s="2">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F135" s="2"/>
     </row>
@@ -22937,10 +24138,10 @@
         <v>1007</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="E136" s="2">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F136" s="2"/>
     </row>
@@ -22958,7 +24159,7 @@
         <v>1028</v>
       </c>
       <c r="E137" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F137" s="2"/>
     </row>
@@ -22976,7 +24177,7 @@
         <v>1028</v>
       </c>
       <c r="E138" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F138" s="2"/>
     </row>
@@ -22988,7 +24189,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="50" customWidth="1"/>
@@ -23006,16 +24207,16 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1024</v>
@@ -23024,16 +24225,121 @@
         <v>50</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1038</v>
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -23043,6 +24349,53 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="2" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="6" width="11" customWidth="1"/>
+    <col min="9" max="9" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G129"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -23060,16 +24413,16 @@
         <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1039</v>
+        <v>1063</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1040</v>
+        <v>1064</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>337</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1041</v>
+        <v>1065</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>23</v>
@@ -23098,7 +24451,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1042</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23121,7 +24474,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1042</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23144,7 +24497,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23167,7 +24520,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1042</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23190,7 +24543,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1042</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23213,7 +24566,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1042</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23236,7 +24589,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1042</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23259,7 +24612,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23282,7 +24635,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23305,7 +24658,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23328,7 +24681,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23351,7 +24704,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23374,7 +24727,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23397,7 +24750,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23420,7 +24773,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23443,7 +24796,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23466,7 +24819,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23489,7 +24842,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23512,7 +24865,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23535,7 +24888,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23558,7 +24911,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23581,7 +24934,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23604,7 +24957,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23627,7 +24980,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23650,7 +25003,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23673,7 +25026,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23696,7 +25049,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23719,7 +25072,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23742,7 +25095,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23765,7 +25118,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23788,7 +25141,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23811,7 +25164,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23834,7 +25187,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23857,7 +25210,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23880,7 +25233,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23903,7 +25256,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23926,7 +25279,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23949,7 +25302,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23972,7 +25325,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23995,7 +25348,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24018,7 +25371,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24041,7 +25394,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24064,7 +25417,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24087,7 +25440,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24110,7 +25463,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24133,7 +25486,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24156,7 +25509,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24179,7 +25532,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24202,7 +25555,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24225,7 +25578,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24248,7 +25601,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1042</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24271,7 +25624,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24294,7 +25647,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24317,7 +25670,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24340,7 +25693,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24363,7 +25716,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24386,7 +25739,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="59" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24409,7 +25762,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="60" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24432,7 +25785,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="61" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24455,7 +25808,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="62" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24478,7 +25831,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="63" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24501,7 +25854,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="64" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24524,7 +25877,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="65" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24547,7 +25900,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="66" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24570,7 +25923,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="67" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24593,7 +25946,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="68" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24616,7 +25969,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="69" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24639,7 +25992,7 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="70" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24662,7 +26015,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="71" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24685,7 +26038,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="72" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24708,7 +26061,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="73" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24731,7 +26084,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="74" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24754,7 +26107,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="75" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24777,7 +26130,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="76" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24800,7 +26153,7 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="77" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24823,7 +26176,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="78" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24846,7 +26199,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="79" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24869,7 +26222,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="80" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24892,7 +26245,7 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="81" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24915,7 +26268,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="82" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24938,7 +26291,7 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="83" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24961,7 +26314,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="84" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24984,7 +26337,7 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="85" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25007,7 +26360,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="86" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25030,7 +26383,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="87" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25053,7 +26406,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="88" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25076,7 +26429,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="89" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25099,7 +26452,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="90" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25122,7 +26475,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="91" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25145,7 +26498,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="92" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25168,7 +26521,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="93" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25191,7 +26544,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="94" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25214,7 +26567,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="95" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25237,7 +26590,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="96" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25260,7 +26613,7 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="97" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25283,7 +26636,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="98" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25306,7 +26659,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="99" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25329,7 +26682,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="100" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25352,7 +26705,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="101" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25375,7 +26728,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="102" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25398,7 +26751,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="103" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25421,7 +26774,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="104" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25444,7 +26797,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="105" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25467,7 +26820,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="106" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25490,7 +26843,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="107" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25513,7 +26866,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="108" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25536,7 +26889,7 @@
         <v>0</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="109" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25559,7 +26912,7 @@
         <v>0</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="110" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25582,7 +26935,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25605,7 +26958,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="112" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25628,7 +26981,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="113" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25651,7 +27004,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="114" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25674,7 +27027,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="115" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25697,7 +27050,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="116" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25720,7 +27073,7 @@
         <v>0</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="117" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25743,7 +27096,7 @@
         <v>0</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="118" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25766,7 +27119,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="119" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25789,7 +27142,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="120" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25812,7 +27165,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="121" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25835,7 +27188,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="122" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25858,7 +27211,7 @@
         <v>0</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="123" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25881,7 +27234,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="124" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25901,10 +27254,10 @@
         <v>2</v>
       </c>
       <c r="F124" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>1043</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="125" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25927,7 +27280,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="126" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25947,10 +27300,10 @@
         <v>3</v>
       </c>
       <c r="F126" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>1043</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="127" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25973,7 +27326,7 @@
         <v>0</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="128" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25993,10 +27346,10 @@
         <v>4</v>
       </c>
       <c r="F128" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>1043</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="129" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26019,7 +27372,7 @@
         <v>0</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
     </row>
   </sheetData>
@@ -26028,7 +27381,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -26041,13 +27394,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1045</v>
+        <v>1070</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1046</v>
+        <v>1071</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1047</v>
+        <v>1072</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
@@ -26055,1352 +27408,212 @@
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1048</v>
+        <v>1073</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1049</v>
+        <v>1074</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1050</v>
+        <v>1075</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1051</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1052</v>
+        <v>1077</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1053</v>
+        <v>1078</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1054</v>
+        <v>1079</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1051</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1055</v>
+        <v>1080</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1056</v>
+        <v>1081</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1057</v>
+        <v>1082</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1051</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1058</v>
+        <v>1083</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1059</v>
+        <v>1084</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1060</v>
+        <v>1085</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1051</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1061</v>
+        <v>1087</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1062</v>
+        <v>1088</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1063</v>
+        <v>1089</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1051</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1064</v>
+        <v>1090</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1065</v>
+        <v>1091</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>1000</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1051</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1066</v>
+        <v>1092</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1067</v>
+        <v>1093</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1068</v>
+        <v>1094</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1051</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1069</v>
+        <v>1095</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1070</v>
+        <v>1096</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1071</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1073</v>
+        <v>1099</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1074</v>
+        <v>1100</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1051</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1075</v>
+        <v>1101</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>1076</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1078</v>
+        <v>1104</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1079</v>
+        <v>1105</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>622</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1051</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1080</v>
+        <v>1106</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1081</v>
+        <v>1107</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1082</v>
+        <v>1108</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1051</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1083</v>
+        <v>1109</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1084</v>
+        <v>1110</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1085</v>
+        <v>1111</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1051</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1086</v>
+        <v>1112</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1087</v>
+        <v>1113</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>674</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1051</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>1088</v>
+        <v>1114</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1089</v>
+        <v>1115</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K32"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>1090</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1091</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1093</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1095</v>
-      </c>
-      <c r="E2" s="2">
-        <v>2</v>
-      </c>
-      <c r="F2" s="2">
-        <v>2</v>
-      </c>
-      <c r="G2" s="2">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
         <v>1097</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1099</v>
-      </c>
-      <c r="E3" s="2">
-        <v>4</v>
-      </c>
-      <c r="F3" s="2">
-        <v>4</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>1101</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1097</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1103</v>
-      </c>
-      <c r="E4" s="2">
-        <v>7</v>
-      </c>
-      <c r="F4" s="2">
-        <v>9</v>
-      </c>
-      <c r="G4" s="2">
-        <v>6</v>
-      </c>
-      <c r="H4" s="2">
-        <v>6</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>1104</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1097</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1105</v>
-      </c>
-      <c r="E5" s="2">
-        <v>5</v>
-      </c>
-      <c r="F5" s="2">
-        <v>5</v>
-      </c>
-      <c r="G5" s="2">
-        <v>2</v>
-      </c>
-      <c r="H5" s="2">
-        <v>2</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>1106</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>1097</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1107</v>
-      </c>
-      <c r="E6" s="2">
-        <v>3</v>
-      </c>
-      <c r="F6" s="2">
-        <v>3</v>
-      </c>
-      <c r="G6" s="2">
-        <v>2</v>
-      </c>
-      <c r="H6" s="2">
-        <v>2</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1109</v>
-      </c>
-      <c r="E7" s="2">
-        <v>4</v>
-      </c>
-      <c r="F7" s="2">
-        <v>4</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>1110</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="E8" s="2">
-        <v>5</v>
-      </c>
-      <c r="F8" s="2">
-        <v>5</v>
-      </c>
-      <c r="G8" s="2">
-        <v>5</v>
-      </c>
-      <c r="H8" s="2">
-        <v>5</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>1113</v>
-      </c>
-      <c r="E9" s="2">
-        <v>4</v>
-      </c>
-      <c r="F9" s="2">
-        <v>5</v>
-      </c>
-      <c r="G9" s="2">
-        <v>4</v>
-      </c>
-      <c r="H9" s="2">
-        <v>4</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E10" s="2">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2">
-        <v>4</v>
-      </c>
-      <c r="G10" s="2">
-        <v>2</v>
-      </c>
-      <c r="H10" s="2">
-        <v>2</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>1116</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>1117</v>
-      </c>
-      <c r="E11" s="2">
-        <v>4</v>
-      </c>
-      <c r="F11" s="2">
-        <v>4</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>1118</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1116</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="E12" s="2">
-        <v>7</v>
-      </c>
-      <c r="F12" s="2">
-        <v>7</v>
-      </c>
-      <c r="G12" s="2">
-        <v>2</v>
-      </c>
-      <c r="H12" s="2">
-        <v>2</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>1116</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>1121</v>
-      </c>
-      <c r="E13" s="2">
-        <v>3</v>
-      </c>
-      <c r="F13" s="2">
-        <v>3</v>
-      </c>
-      <c r="G13" s="2">
-        <v>3</v>
-      </c>
-      <c r="H13" s="2">
-        <v>3</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>1116</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>1123</v>
-      </c>
-      <c r="E14" s="2">
-        <v>3</v>
-      </c>
-      <c r="F14" s="2">
-        <v>3</v>
-      </c>
-      <c r="G14" s="2">
-        <v>2</v>
-      </c>
-      <c r="H14" s="2">
-        <v>2</v>
-      </c>
-      <c r="I14" s="2">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>1125</v>
-      </c>
-      <c r="E15" s="2">
-        <v>4</v>
-      </c>
-      <c r="F15" s="2">
-        <v>4</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>1126</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>1127</v>
-      </c>
-      <c r="E16" s="2">
-        <v>5</v>
-      </c>
-      <c r="F16" s="2">
-        <v>5</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2">
-        <v>1</v>
-      </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>1129</v>
-      </c>
-      <c r="E17" s="2">
-        <v>4</v>
-      </c>
-      <c r="F17" s="2">
-        <v>4</v>
-      </c>
-      <c r="G17" s="2">
-        <v>2</v>
-      </c>
-      <c r="H17" s="2">
-        <v>2</v>
-      </c>
-      <c r="I17" s="2">
-        <v>0</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="E18" s="2">
-        <v>5</v>
-      </c>
-      <c r="F18" s="2">
-        <v>5</v>
-      </c>
-      <c r="G18" s="2">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2">
-        <v>1</v>
-      </c>
-      <c r="I18" s="2">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>1133</v>
-      </c>
-      <c r="E19" s="2">
-        <v>4</v>
-      </c>
-      <c r="F19" s="2">
-        <v>4</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>1134</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>1135</v>
-      </c>
-      <c r="E20" s="2">
-        <v>6</v>
-      </c>
-      <c r="F20" s="2">
-        <v>6</v>
-      </c>
-      <c r="G20" s="2">
-        <v>4</v>
-      </c>
-      <c r="H20" s="2">
-        <v>4</v>
-      </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>1136</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>1137</v>
-      </c>
-      <c r="E21" s="2">
-        <v>6</v>
-      </c>
-      <c r="F21" s="2">
-        <v>9</v>
-      </c>
-      <c r="G21" s="2">
-        <v>6</v>
-      </c>
-      <c r="H21" s="2">
-        <v>6</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>1139</v>
-      </c>
-      <c r="E22" s="2">
-        <v>6</v>
-      </c>
-      <c r="F22" s="2">
-        <v>6</v>
-      </c>
-      <c r="G22" s="2">
-        <v>3</v>
-      </c>
-      <c r="H22" s="2">
-        <v>3</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>1141</v>
-      </c>
-      <c r="E23" s="2">
-        <v>3</v>
-      </c>
-      <c r="F23" s="2">
-        <v>3</v>
-      </c>
-      <c r="G23" s="2">
-        <v>3</v>
-      </c>
-      <c r="H23" s="2">
-        <v>3</v>
-      </c>
-      <c r="I23" s="2">
-        <v>0</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>1142</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>1143</v>
-      </c>
-      <c r="E24" s="2">
-        <v>4</v>
-      </c>
-      <c r="F24" s="2">
-        <v>4</v>
-      </c>
-      <c r="G24" s="2">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2">
-        <v>0</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>1144</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1142</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>1145</v>
-      </c>
-      <c r="E25" s="2">
-        <v>5</v>
-      </c>
-      <c r="F25" s="2">
-        <v>5</v>
-      </c>
-      <c r="G25" s="2">
-        <v>3</v>
-      </c>
-      <c r="H25" s="2">
-        <v>3</v>
-      </c>
-      <c r="I25" s="2">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>1146</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>1142</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>1147</v>
-      </c>
-      <c r="E26" s="2">
-        <v>5</v>
-      </c>
-      <c r="F26" s="2">
-        <v>5</v>
-      </c>
-      <c r="G26" s="2">
-        <v>1</v>
-      </c>
-      <c r="H26" s="2">
-        <v>1</v>
-      </c>
-      <c r="I26" s="2">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>1142</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>1149</v>
-      </c>
-      <c r="E27" s="2">
-        <v>3</v>
-      </c>
-      <c r="F27" s="2">
-        <v>3</v>
-      </c>
-      <c r="G27" s="2">
-        <v>1</v>
-      </c>
-      <c r="H27" s="2">
-        <v>1</v>
-      </c>
-      <c r="I27" s="2">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>1150</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>1151</v>
-      </c>
-      <c r="E28" s="2">
-        <v>4</v>
-      </c>
-      <c r="F28" s="2">
-        <v>4</v>
-      </c>
-      <c r="G28" s="2">
-        <v>0</v>
-      </c>
-      <c r="H28" s="2">
-        <v>0</v>
-      </c>
-      <c r="I28" s="2">
-        <v>0</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>1150</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>1153</v>
-      </c>
-      <c r="E29" s="2">
-        <v>5</v>
-      </c>
-      <c r="F29" s="2">
-        <v>5</v>
-      </c>
-      <c r="G29" s="2">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2">
-        <v>1</v>
-      </c>
-      <c r="I29" s="2">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>1154</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>1150</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>1155</v>
-      </c>
-      <c r="E30" s="2">
-        <v>6</v>
-      </c>
-      <c r="F30" s="2">
-        <v>6</v>
-      </c>
-      <c r="G30" s="2">
-        <v>1</v>
-      </c>
-      <c r="H30" s="2">
-        <v>1</v>
-      </c>
-      <c r="I30" s="2">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>1156</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>1150</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>1157</v>
-      </c>
-      <c r="E31" s="2">
-        <v>4</v>
-      </c>
-      <c r="F31" s="2">
-        <v>4</v>
-      </c>
-      <c r="G31" s="2">
-        <v>1</v>
-      </c>
-      <c r="H31" s="2">
-        <v>1</v>
-      </c>
-      <c r="I31" s="2">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>1150</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>1159</v>
-      </c>
-      <c r="E32" s="2">
-        <v>4</v>
-      </c>
-      <c r="F32" s="2">
-        <v>4</v>
-      </c>
-      <c r="G32" s="2">
-        <v>0</v>
-      </c>
-      <c r="H32" s="2">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2">
-        <v>0</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>1100</v>
       </c>
     </row>
   </sheetData>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/09-report/CYC-2-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/09-report/CYC-2-cycle-report.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5810" uniqueCount="1604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5842" uniqueCount="1606">
   <si>
     <t>Metric</t>
   </si>
@@ -170,7 +170,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-02T20:04:55.461Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-02T20:25:59.721Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -3433,6 +3433,9 @@
     <t>Level</t>
   </si>
   <si>
+    <t>Scope</t>
+  </si>
+  <si>
     <t>Parent</t>
   </si>
   <si>
@@ -3442,6 +3445,9 @@
     <t>initiative</t>
   </si>
   <si>
+    <t>this cycle</t>
+  </si>
+  <si>
     <t>[Initiative] Intelligent Hotel Shopping and Reservation Experience</t>
   </si>
   <si>
@@ -4627,7 +4633,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T20:04:56.274Z</t>
+    <t>2026-10-02T20:26:00.496Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -5461,19 +5467,19 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="1" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="8" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1116</v>
       </c>
@@ -5487,83 +5493,89 @@
         <v>1119</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>339</v>
+        <v>1122</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1121</v>
-      </c>
-      <c r="E2" s="2">
-        <v>2</v>
+        <v>339</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1123</v>
       </c>
       <c r="F2" s="2">
         <v>2</v>
       </c>
       <c r="G2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="2">
         <v>1</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>339</v>
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>1123</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>1125</v>
-      </c>
-      <c r="E3" s="2">
-        <v>4</v>
+      <c r="E3" s="2" t="s">
+        <v>1127</v>
       </c>
       <c r="F3" s="2">
         <v>4</v>
       </c>
       <c r="G3" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" s="2">
         <v>0</v>
@@ -5571,139 +5583,151 @@
       <c r="I3" s="2">
         <v>0</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>339</v>
+      <c r="J3" s="2">
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1129</v>
-      </c>
-      <c r="E4" s="2">
+        <v>1125</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F4" s="2">
         <v>7</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="2">
         <v>9</v>
-      </c>
-      <c r="G4" s="2">
-        <v>6</v>
       </c>
       <c r="H4" s="2">
         <v>6</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>339</v>
+        <v>6</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>1057</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F5" s="2">
+        <v>8</v>
+      </c>
+      <c r="G5" s="2">
+        <v>15</v>
+      </c>
+      <c r="H5" s="2">
+        <v>12</v>
+      </c>
+      <c r="I5" s="2">
+        <v>11</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="E5" s="2">
-        <v>8</v>
-      </c>
-      <c r="F5" s="2">
-        <v>15</v>
-      </c>
-      <c r="G5" s="2">
-        <v>12</v>
-      </c>
-      <c r="H5" s="2">
-        <v>11</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>1055</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>1128</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1133</v>
-      </c>
-      <c r="E6" s="2">
-        <v>3</v>
+        <v>1125</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>1135</v>
       </c>
       <c r="F6" s="2">
         <v>3</v>
       </c>
       <c r="G6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" s="2">
         <v>2</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>339</v>
+        <v>2</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>1134</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>1135</v>
-      </c>
-      <c r="E7" s="2">
-        <v>4</v>
+      <c r="E7" s="2" t="s">
+        <v>1137</v>
       </c>
       <c r="F7" s="2">
         <v>4</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
@@ -5711,28 +5735,31 @@
       <c r="I7" s="2">
         <v>0</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>339</v>
+      <c r="J7" s="2">
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>1136</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>1134</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>1137</v>
-      </c>
-      <c r="E8" s="2">
-        <v>5</v>
+      <c r="E8" s="2" t="s">
+        <v>1139</v>
       </c>
       <c r="F8" s="2">
         <v>5</v>
@@ -5744,106 +5771,115 @@
         <v>5</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>339</v>
+        <v>5</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1134</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>1139</v>
-      </c>
-      <c r="E9" s="2">
+        <v>1136</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F9" s="2">
         <v>4</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G9" s="2">
         <v>5</v>
-      </c>
-      <c r="G9" s="2">
-        <v>4</v>
       </c>
       <c r="H9" s="2">
         <v>4</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>339</v>
+        <v>4</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1134</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>1141</v>
-      </c>
-      <c r="E10" s="2">
-        <v>4</v>
+        <v>1136</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>1143</v>
       </c>
       <c r="F10" s="2">
         <v>4</v>
       </c>
       <c r="G10" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10" s="2">
         <v>2</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>339</v>
+        <v>2</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>1142</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>1143</v>
-      </c>
-      <c r="E11" s="2">
-        <v>4</v>
+      <c r="E11" s="2" t="s">
+        <v>1145</v>
       </c>
       <c r="F11" s="2">
         <v>4</v>
       </c>
       <c r="G11" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11" s="2">
         <v>0</v>
@@ -5851,63 +5887,69 @@
       <c r="I11" s="2">
         <v>0</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>339</v>
+      <c r="J11" s="2">
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1142</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>1145</v>
-      </c>
-      <c r="E12" s="2">
-        <v>7</v>
+      <c r="E12" s="2" t="s">
+        <v>1147</v>
       </c>
       <c r="F12" s="2">
         <v>7</v>
       </c>
       <c r="G12" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H12" s="2">
         <v>2</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>339</v>
+        <v>2</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>1146</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>1142</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>1147</v>
-      </c>
-      <c r="E13" s="2">
-        <v>3</v>
+        <v>1144</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>1149</v>
       </c>
       <c r="F13" s="2">
         <v>3</v>
@@ -5919,71 +5961,77 @@
         <v>3</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>339</v>
+        <v>3</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>1142</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>1149</v>
-      </c>
-      <c r="E14" s="2">
-        <v>3</v>
+        <v>1144</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>1151</v>
       </c>
       <c r="F14" s="2">
         <v>3</v>
       </c>
       <c r="G14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="2">
         <v>2</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>339</v>
+        <v>2</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>1150</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>1151</v>
-      </c>
-      <c r="E15" s="2">
-        <v>4</v>
+      <c r="E15" s="2" t="s">
+        <v>1153</v>
       </c>
       <c r="F15" s="2">
         <v>4</v>
       </c>
       <c r="G15" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H15" s="2">
         <v>0</v>
@@ -5991,139 +6039,151 @@
       <c r="I15" s="2">
         <v>0</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>339</v>
+      <c r="J15" s="2">
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>1152</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1150</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>1153</v>
-      </c>
-      <c r="E16" s="2">
-        <v>6</v>
+      <c r="E16" s="2" t="s">
+        <v>1155</v>
       </c>
       <c r="F16" s="2">
         <v>6</v>
       </c>
       <c r="G16" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H16" s="2">
         <v>2</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>339</v>
+        <v>2</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>1154</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>1150</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>1155</v>
-      </c>
-      <c r="E17" s="2">
-        <v>4</v>
+        <v>1152</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>1157</v>
       </c>
       <c r="F17" s="2">
         <v>4</v>
       </c>
       <c r="G17" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17" s="2">
         <v>2</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>339</v>
+        <v>2</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>1043</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1150</v>
+        <v>1122</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1156</v>
-      </c>
-      <c r="E18" s="2">
+        <v>1152</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F18" s="2">
         <v>6</v>
       </c>
-      <c r="F18" s="2">
+      <c r="G18" s="2">
         <v>7</v>
       </c>
-      <c r="G18" s="2">
+      <c r="H18" s="2">
         <v>3</v>
       </c>
-      <c r="H18" s="2">
+      <c r="I18" s="2">
         <v>2</v>
       </c>
-      <c r="I18" s="2">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" s="2">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2" t="s">
         <v>1040</v>
       </c>
-      <c r="K18" s="2" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L18" s="2" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>1158</v>
-      </c>
-      <c r="E19" s="2">
-        <v>4</v>
+      <c r="E19" s="2" t="s">
+        <v>1160</v>
       </c>
       <c r="F19" s="2">
         <v>4</v>
       </c>
       <c r="G19" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" s="2">
         <v>0</v>
@@ -6131,133 +6191,145 @@
       <c r="I19" s="2">
         <v>0</v>
       </c>
-      <c r="J19" s="2" t="s">
-        <v>339</v>
+      <c r="J19" s="2">
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>1159</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>1157</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>1160</v>
-      </c>
-      <c r="E20" s="2">
-        <v>6</v>
+      <c r="E20" s="2" t="s">
+        <v>1162</v>
       </c>
       <c r="F20" s="2">
         <v>6</v>
       </c>
       <c r="G20" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H20" s="2">
         <v>4</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>339</v>
+        <v>4</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>1161</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1157</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>1162</v>
-      </c>
-      <c r="E21" s="2">
+        <v>1159</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F21" s="2">
         <v>6</v>
       </c>
-      <c r="F21" s="2">
+      <c r="G21" s="2">
         <v>9</v>
-      </c>
-      <c r="G21" s="2">
-        <v>6</v>
       </c>
       <c r="H21" s="2">
         <v>6</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>339</v>
+        <v>6</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>1050</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1157</v>
+        <v>1122</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1163</v>
-      </c>
-      <c r="E22" s="2">
+        <v>1159</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F22" s="2">
         <v>7</v>
       </c>
-      <c r="F22" s="2">
+      <c r="G22" s="2">
         <v>9</v>
       </c>
-      <c r="G22" s="2">
+      <c r="H22" s="2">
         <v>6</v>
       </c>
-      <c r="H22" s="2">
+      <c r="I22" s="2">
         <v>5</v>
       </c>
-      <c r="I22" s="2">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2" t="s">
+      <c r="J22" s="2">
+        <v>1</v>
+      </c>
+      <c r="K22" s="2" t="s">
         <v>1048</v>
       </c>
-      <c r="K22" s="2" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L22" s="2" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1157</v>
+        <v>1122</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1165</v>
-      </c>
-      <c r="E23" s="2">
-        <v>3</v>
+        <v>1159</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>1167</v>
       </c>
       <c r="F23" s="2">
         <v>3</v>
@@ -6269,36 +6341,39 @@
         <v>3</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>339</v>
+        <v>3</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>1166</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>1167</v>
-      </c>
-      <c r="E24" s="2">
-        <v>4</v>
+      <c r="E24" s="2" t="s">
+        <v>1169</v>
       </c>
       <c r="F24" s="2">
         <v>4</v>
       </c>
       <c r="G24" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H24" s="2">
         <v>0</v>
@@ -6306,139 +6381,151 @@
       <c r="I24" s="2">
         <v>0</v>
       </c>
-      <c r="J24" s="2" t="s">
-        <v>339</v>
+      <c r="J24" s="2">
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>1168</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1166</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>1169</v>
-      </c>
-      <c r="E25" s="2">
-        <v>5</v>
+      <c r="E25" s="2" t="s">
+        <v>1171</v>
       </c>
       <c r="F25" s="2">
         <v>5</v>
       </c>
       <c r="G25" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H25" s="2">
         <v>3</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>339</v>
+        <v>3</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0</v>
       </c>
       <c r="K25" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>1170</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>1166</v>
-      </c>
       <c r="D26" s="2" t="s">
-        <v>1171</v>
-      </c>
-      <c r="E26" s="2">
-        <v>5</v>
+        <v>1168</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>1173</v>
       </c>
       <c r="F26" s="2">
         <v>5</v>
       </c>
       <c r="G26" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>339</v>
+        <v>1</v>
+      </c>
+      <c r="J26" s="2">
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>1166</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>1173</v>
-      </c>
-      <c r="E27" s="2">
-        <v>4</v>
+        <v>1168</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>1175</v>
       </c>
       <c r="F27" s="2">
         <v>4</v>
       </c>
       <c r="G27" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H27" s="2">
         <v>2</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>339</v>
+        <v>2</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0</v>
       </c>
       <c r="K27" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>1174</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>1175</v>
-      </c>
-      <c r="E28" s="2">
-        <v>4</v>
+      <c r="E28" s="2" t="s">
+        <v>1177</v>
       </c>
       <c r="F28" s="2">
         <v>4</v>
       </c>
       <c r="G28" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H28" s="2">
         <v>0</v>
@@ -6446,139 +6533,151 @@
       <c r="I28" s="2">
         <v>0</v>
       </c>
-      <c r="J28" s="2" t="s">
-        <v>339</v>
+      <c r="J28" s="2">
+        <v>0</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>1176</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>1174</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>1177</v>
-      </c>
-      <c r="E29" s="2">
-        <v>5</v>
+      <c r="E29" s="2" t="s">
+        <v>1179</v>
       </c>
       <c r="F29" s="2">
         <v>5</v>
       </c>
       <c r="G29" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>339</v>
+        <v>1</v>
+      </c>
+      <c r="J29" s="2">
+        <v>0</v>
       </c>
       <c r="K29" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>1178</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>1174</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>1179</v>
-      </c>
-      <c r="E30" s="2">
-        <v>6</v>
+        <v>1176</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>1181</v>
       </c>
       <c r="F30" s="2">
         <v>6</v>
       </c>
       <c r="G30" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
       </c>
       <c r="I30" s="2">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>339</v>
+        <v>1</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0</v>
       </c>
       <c r="K30" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>1180</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>1174</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>1181</v>
-      </c>
-      <c r="E31" s="2">
-        <v>4</v>
+        <v>1176</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>1183</v>
       </c>
       <c r="F31" s="2">
         <v>4</v>
       </c>
       <c r="G31" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
       </c>
       <c r="I31" s="2">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>339</v>
+        <v>1</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0</v>
       </c>
       <c r="K31" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>1174</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>1183</v>
-      </c>
-      <c r="E32" s="2">
-        <v>4</v>
+        <v>1176</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>1185</v>
       </c>
       <c r="F32" s="2">
         <v>4</v>
       </c>
       <c r="G32" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H32" s="2">
         <v>0</v>
@@ -6586,11 +6685,14 @@
       <c r="I32" s="2">
         <v>0</v>
       </c>
-      <c r="J32" s="2" t="s">
-        <v>339</v>
+      <c r="J32" s="2">
+        <v>0</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>1126</v>
+        <v>339</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>1128</v>
       </c>
     </row>
   </sheetData>
@@ -6619,19 +6721,19 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>314</v>
@@ -6640,19 +6742,19 @@
         <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>1025</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>1035</v>
@@ -6669,7 +6771,7 @@
         <v>61</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>326</v>
@@ -6684,10 +6786,10 @@
         <v>337</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>1028</v>
@@ -6710,7 +6812,7 @@
         <v>71</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>340</v>
@@ -6725,7 +6827,7 @@
         <v>348</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
@@ -6749,7 +6851,7 @@
         <v>73</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>349</v>
@@ -6764,7 +6866,7 @@
         <v>348</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
@@ -6788,7 +6890,7 @@
         <v>75</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>353</v>
@@ -6803,7 +6905,7 @@
         <v>348</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
@@ -6827,7 +6929,7 @@
         <v>77</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>357</v>
@@ -6842,7 +6944,7 @@
         <v>348</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
@@ -6866,7 +6968,7 @@
         <v>79</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>361</v>
@@ -6881,7 +6983,7 @@
         <v>348</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
@@ -6896,7 +6998,7 @@
     </row>
     <row r="8" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>80</v>
@@ -6905,7 +7007,7 @@
         <v>81</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>365</v>
@@ -6920,10 +7022,10 @@
         <v>337</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>1028</v>
@@ -6937,7 +7039,7 @@
     </row>
     <row r="9" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>82</v>
@@ -6946,7 +7048,7 @@
         <v>83</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>373</v>
@@ -6961,10 +7063,10 @@
         <v>337</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>1028</v>
@@ -6978,7 +7080,7 @@
     </row>
     <row r="10" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>84</v>
@@ -6987,7 +7089,7 @@
         <v>85</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>379</v>
@@ -7002,10 +7104,10 @@
         <v>337</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>1028</v>
@@ -7019,7 +7121,7 @@
     </row>
     <row r="11" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>84</v>
@@ -7028,7 +7130,7 @@
         <v>85</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>386</v>
@@ -7043,10 +7145,10 @@
         <v>337</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>1028</v>
@@ -7060,7 +7162,7 @@
     </row>
     <row r="12" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>84</v>
@@ -7069,7 +7171,7 @@
         <v>85</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>392</v>
@@ -7084,10 +7186,10 @@
         <v>337</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>1215</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>1213</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>1028</v>
@@ -7101,7 +7203,7 @@
     </row>
     <row r="13" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>86</v>
@@ -7110,7 +7212,7 @@
         <v>87</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>398</v>
@@ -7125,10 +7227,10 @@
         <v>337</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>1028</v>
@@ -7142,7 +7244,7 @@
     </row>
     <row r="14" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>89</v>
@@ -7151,7 +7253,7 @@
         <v>90</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>407</v>
@@ -7166,7 +7268,7 @@
         <v>348</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
@@ -7181,7 +7283,7 @@
     </row>
     <row r="15" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>91</v>
@@ -7190,7 +7292,7 @@
         <v>92</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>411</v>
@@ -7205,7 +7307,7 @@
         <v>348</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
@@ -7220,7 +7322,7 @@
     </row>
     <row r="16" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>93</v>
@@ -7229,7 +7331,7 @@
         <v>94</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>415</v>
@@ -7244,7 +7346,7 @@
         <v>348</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
@@ -7268,7 +7370,7 @@
         <v>96</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>419</v>
@@ -7283,10 +7385,10 @@
         <v>337</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>1028</v>
@@ -7309,7 +7411,7 @@
         <v>98</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>425</v>
@@ -7324,10 +7426,10 @@
         <v>337</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>1028</v>
@@ -7350,7 +7452,7 @@
         <v>100</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>432</v>
@@ -7365,7 +7467,7 @@
         <v>348</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
@@ -7389,7 +7491,7 @@
         <v>102</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>436</v>
@@ -7404,7 +7506,7 @@
         <v>348</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
@@ -7428,7 +7530,7 @@
         <v>104</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>440</v>
@@ -7443,7 +7545,7 @@
         <v>348</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2" t="s">
@@ -7458,7 +7560,7 @@
     </row>
     <row r="22" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>105</v>
@@ -7467,7 +7569,7 @@
         <v>106</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>444</v>
@@ -7482,10 +7584,10 @@
         <v>337</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>1028</v>
@@ -7499,7 +7601,7 @@
     </row>
     <row r="23" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>107</v>
@@ -7508,7 +7610,7 @@
         <v>108</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>446</v>
@@ -7523,7 +7625,7 @@
         <v>348</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
@@ -7538,7 +7640,7 @@
     </row>
     <row r="24" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>109</v>
@@ -7547,7 +7649,7 @@
         <v>110</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>450</v>
@@ -7562,10 +7664,10 @@
         <v>337</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>1028</v>
@@ -7579,7 +7681,7 @@
     </row>
     <row r="25" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>111</v>
@@ -7588,7 +7690,7 @@
         <v>112</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>456</v>
@@ -7603,10 +7705,10 @@
         <v>337</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>1028</v>
@@ -7620,7 +7722,7 @@
     </row>
     <row r="26" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>113</v>
@@ -7629,7 +7731,7 @@
         <v>114</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>462</v>
@@ -7644,10 +7746,10 @@
         <v>337</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>1028</v>
@@ -7661,7 +7763,7 @@
     </row>
     <row r="27" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>115</v>
@@ -7670,7 +7772,7 @@
         <v>116</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>467</v>
@@ -7685,10 +7787,10 @@
         <v>337</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>1028</v>
@@ -7702,7 +7804,7 @@
     </row>
     <row r="28" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>117</v>
@@ -7711,7 +7813,7 @@
         <v>118</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>475</v>
@@ -7726,10 +7828,10 @@
         <v>337</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>1028</v>
@@ -7743,7 +7845,7 @@
     </row>
     <row r="29" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>119</v>
@@ -7752,7 +7854,7 @@
         <v>120</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>481</v>
@@ -7767,10 +7869,10 @@
         <v>337</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>1028</v>
@@ -7784,7 +7886,7 @@
     </row>
     <row r="30" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>121</v>
@@ -7793,7 +7895,7 @@
         <v>122</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>488</v>
@@ -7808,10 +7910,10 @@
         <v>337</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>1028</v>
@@ -7825,7 +7927,7 @@
     </row>
     <row r="31" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>123</v>
@@ -7834,7 +7936,7 @@
         <v>124</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>494</v>
@@ -7849,10 +7951,10 @@
         <v>337</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>1028</v>
@@ -7866,7 +7968,7 @@
     </row>
     <row r="32" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>123</v>
@@ -7875,7 +7977,7 @@
         <v>124</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>500</v>
@@ -7890,10 +7992,10 @@
         <v>337</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>1028</v>
@@ -7907,7 +8009,7 @@
     </row>
     <row r="33" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>125</v>
@@ -7916,7 +8018,7 @@
         <v>126</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>505</v>
@@ -7931,7 +8033,7 @@
         <v>348</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
@@ -7946,7 +8048,7 @@
     </row>
     <row r="34" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>127</v>
@@ -7955,7 +8057,7 @@
         <v>128</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>509</v>
@@ -7970,10 +8072,10 @@
         <v>337</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>1028</v>
@@ -7987,7 +8089,7 @@
     </row>
     <row r="35" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>129</v>
@@ -7996,7 +8098,7 @@
         <v>130</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>515</v>
@@ -8011,10 +8113,10 @@
         <v>337</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>1028</v>
@@ -8028,7 +8130,7 @@
     </row>
     <row r="36" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>131</v>
@@ -8037,7 +8139,7 @@
         <v>132</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>521</v>
@@ -8052,7 +8154,7 @@
         <v>348</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
@@ -8067,7 +8169,7 @@
     </row>
     <row r="37" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>133</v>
@@ -8076,7 +8178,7 @@
         <v>134</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>525</v>
@@ -8091,7 +8193,7 @@
         <v>348</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
@@ -8106,7 +8208,7 @@
     </row>
     <row r="38" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>135</v>
@@ -8115,7 +8217,7 @@
         <v>136</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>529</v>
@@ -8130,10 +8232,10 @@
         <v>337</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>1028</v>
@@ -8147,7 +8249,7 @@
     </row>
     <row r="39" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>137</v>
@@ -8156,7 +8258,7 @@
         <v>138</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>535</v>
@@ -8171,7 +8273,7 @@
         <v>348</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
@@ -8186,7 +8288,7 @@
     </row>
     <row r="40" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>139</v>
@@ -8195,7 +8297,7 @@
         <v>140</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>539</v>
@@ -8210,10 +8312,10 @@
         <v>337</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>1028</v>
@@ -8227,7 +8329,7 @@
     </row>
     <row r="41" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>141</v>
@@ -8236,7 +8338,7 @@
         <v>142</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>545</v>
@@ -8251,10 +8353,10 @@
         <v>337</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>1028</v>
@@ -8268,7 +8370,7 @@
     </row>
     <row r="42" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>143</v>
@@ -8277,7 +8379,7 @@
         <v>144</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>551</v>
@@ -8292,7 +8394,7 @@
         <v>348</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
@@ -8307,7 +8409,7 @@
     </row>
     <row r="43" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>145</v>
@@ -8316,7 +8418,7 @@
         <v>146</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>555</v>
@@ -8331,7 +8433,7 @@
         <v>348</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
@@ -8346,7 +8448,7 @@
     </row>
     <row r="44" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>147</v>
@@ -8355,7 +8457,7 @@
         <v>148</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>559</v>
@@ -8370,7 +8472,7 @@
         <v>348</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
@@ -8385,7 +8487,7 @@
     </row>
     <row r="45" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>149</v>
@@ -8394,7 +8496,7 @@
         <v>150</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>563</v>
@@ -8409,7 +8511,7 @@
         <v>348</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
@@ -8424,7 +8526,7 @@
     </row>
     <row r="46" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>151</v>
@@ -8433,7 +8535,7 @@
         <v>152</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>567</v>
@@ -8448,10 +8550,10 @@
         <v>337</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>1028</v>
@@ -8465,7 +8567,7 @@
     </row>
     <row r="47" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>153</v>
@@ -8474,7 +8576,7 @@
         <v>154</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>572</v>
@@ -8489,10 +8591,10 @@
         <v>337</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>1028</v>
@@ -8506,7 +8608,7 @@
     </row>
     <row r="48" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>155</v>
@@ -8515,7 +8617,7 @@
         <v>156</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>578</v>
@@ -8530,10 +8632,10 @@
         <v>337</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>1028</v>
@@ -8547,7 +8649,7 @@
     </row>
     <row r="49" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>159</v>
@@ -8556,7 +8658,7 @@
         <v>160</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>580</v>
@@ -8571,7 +8673,7 @@
         <v>348</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
@@ -8586,7 +8688,7 @@
     </row>
     <row r="50" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>161</v>
@@ -8595,7 +8697,7 @@
         <v>162</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>584</v>
@@ -8610,10 +8712,10 @@
         <v>337</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>1028</v>
@@ -8627,7 +8729,7 @@
     </row>
     <row r="51" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>163</v>
@@ -8636,7 +8738,7 @@
         <v>164</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>590</v>
@@ -8651,10 +8753,10 @@
         <v>337</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>1028</v>
@@ -8668,7 +8770,7 @@
     </row>
     <row r="52" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>165</v>
@@ -8677,7 +8779,7 @@
         <v>166</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>596</v>
@@ -8692,10 +8794,10 @@
         <v>337</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>1028</v>
@@ -8709,7 +8811,7 @@
     </row>
     <row r="53" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>167</v>
@@ -8718,7 +8820,7 @@
         <v>168</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>602</v>
@@ -8733,7 +8835,7 @@
         <v>348</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
@@ -8748,7 +8850,7 @@
     </row>
     <row r="54" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>169</v>
@@ -8757,7 +8859,7 @@
         <v>170</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>606</v>
@@ -8772,7 +8874,7 @@
         <v>348</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
@@ -8787,7 +8889,7 @@
     </row>
     <row r="55" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>171</v>
@@ -8796,7 +8898,7 @@
         <v>172</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>610</v>
@@ -8811,7 +8913,7 @@
         <v>348</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
@@ -8826,7 +8928,7 @@
     </row>
     <row r="56" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>173</v>
@@ -8835,7 +8937,7 @@
         <v>174</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>614</v>
@@ -8850,7 +8952,7 @@
         <v>348</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
@@ -8865,7 +8967,7 @@
     </row>
     <row r="57" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>175</v>
@@ -8874,7 +8976,7 @@
         <v>176</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>618</v>
@@ -8889,7 +8991,7 @@
         <v>348</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
@@ -8904,7 +9006,7 @@
     </row>
     <row r="58" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>177</v>
@@ -8913,7 +9015,7 @@
         <v>178</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>622</v>
@@ -8928,10 +9030,10 @@
         <v>337</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>1028</v>
@@ -8945,7 +9047,7 @@
     </row>
     <row r="59" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>179</v>
@@ -8954,7 +9056,7 @@
         <v>180</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>629</v>
@@ -8969,10 +9071,10 @@
         <v>337</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>1028</v>
@@ -8986,7 +9088,7 @@
     </row>
     <row r="60" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>181</v>
@@ -8995,7 +9097,7 @@
         <v>182</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>636</v>
@@ -9010,7 +9112,7 @@
         <v>348</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
@@ -9034,7 +9136,7 @@
         <v>184</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>640</v>
@@ -9049,10 +9151,10 @@
         <v>337</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>1028</v>
@@ -9075,7 +9177,7 @@
         <v>186</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>646</v>
@@ -9090,7 +9192,7 @@
         <v>348</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
@@ -9114,7 +9216,7 @@
         <v>188</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>650</v>
@@ -9129,7 +9231,7 @@
         <v>348</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
@@ -9153,7 +9255,7 @@
         <v>190</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>654</v>
@@ -9168,7 +9270,7 @@
         <v>348</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
@@ -9192,7 +9294,7 @@
         <v>192</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>658</v>
@@ -9207,7 +9309,7 @@
         <v>348</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
@@ -9222,7 +9324,7 @@
     </row>
     <row r="66" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>193</v>
@@ -9231,7 +9333,7 @@
         <v>194</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>662</v>
@@ -9246,10 +9348,10 @@
         <v>337</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>1028</v>
@@ -9263,7 +9365,7 @@
     </row>
     <row r="67" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>195</v>
@@ -9272,7 +9374,7 @@
         <v>196</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>667</v>
@@ -9287,10 +9389,10 @@
         <v>337</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>1028</v>
@@ -9304,7 +9406,7 @@
     </row>
     <row r="68" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>197</v>
@@ -9313,7 +9415,7 @@
         <v>198</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>674</v>
@@ -9328,10 +9430,10 @@
         <v>337</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>1028</v>
@@ -9345,7 +9447,7 @@
     </row>
     <row r="69" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>199</v>
@@ -9354,7 +9456,7 @@
         <v>200</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>681</v>
@@ -9369,7 +9471,7 @@
         <v>348</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
@@ -9384,7 +9486,7 @@
     </row>
     <row r="70" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>201</v>
@@ -9393,7 +9495,7 @@
         <v>202</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>685</v>
@@ -9408,7 +9510,7 @@
         <v>348</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
@@ -9423,7 +9525,7 @@
     </row>
     <row r="71" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>203</v>
@@ -9432,7 +9534,7 @@
         <v>204</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>689</v>
@@ -9447,10 +9549,10 @@
         <v>337</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>1028</v>
@@ -9464,7 +9566,7 @@
     </row>
     <row r="72" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>205</v>
@@ -9473,7 +9575,7 @@
         <v>206</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>695</v>
@@ -9488,10 +9590,10 @@
         <v>337</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>1028</v>
@@ -9505,7 +9607,7 @@
     </row>
     <row r="73" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>205</v>
@@ -9514,7 +9616,7 @@
         <v>206</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>702</v>
@@ -9529,10 +9631,10 @@
         <v>337</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>1028</v>
@@ -9546,7 +9648,7 @@
     </row>
     <row r="74" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>207</v>
@@ -9555,7 +9657,7 @@
         <v>208</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>708</v>
@@ -9570,7 +9672,7 @@
         <v>348</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
@@ -9585,7 +9687,7 @@
     </row>
     <row r="75" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>209</v>
@@ -9594,7 +9696,7 @@
         <v>210</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>712</v>
@@ -9609,10 +9711,10 @@
         <v>337</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>1028</v>
@@ -9626,7 +9728,7 @@
     </row>
     <row r="76" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>209</v>
@@ -9635,7 +9737,7 @@
         <v>210</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>719</v>
@@ -9650,10 +9752,10 @@
         <v>337</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>1028</v>
@@ -9667,7 +9769,7 @@
     </row>
     <row r="77" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>209</v>
@@ -9676,7 +9778,7 @@
         <v>210</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>725</v>
@@ -9691,10 +9793,10 @@
         <v>337</v>
       </c>
       <c r="I77" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="J77" s="2" t="s">
         <v>1373</v>
-      </c>
-      <c r="J77" s="2" t="s">
-        <v>1371</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>1028</v>
@@ -9708,7 +9810,7 @@
     </row>
     <row r="78" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>211</v>
@@ -9717,7 +9819,7 @@
         <v>212</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>731</v>
@@ -9732,10 +9834,10 @@
         <v>337</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>1028</v>
@@ -9749,7 +9851,7 @@
     </row>
     <row r="79" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>213</v>
@@ -9758,7 +9860,7 @@
         <v>214</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>738</v>
@@ -9773,7 +9875,7 @@
         <v>348</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
@@ -9788,7 +9890,7 @@
     </row>
     <row r="80" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>215</v>
@@ -9797,7 +9899,7 @@
         <v>216</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>742</v>
@@ -9812,7 +9914,7 @@
         <v>348</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
@@ -9836,7 +9938,7 @@
         <v>218</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>746</v>
@@ -9851,10 +9953,10 @@
         <v>337</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>1028</v>
@@ -9877,7 +9979,7 @@
         <v>220</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>752</v>
@@ -9892,10 +9994,10 @@
         <v>337</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>1028</v>
@@ -9918,7 +10020,7 @@
         <v>222</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>758</v>
@@ -9933,10 +10035,10 @@
         <v>337</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>1028</v>
@@ -9959,7 +10061,7 @@
         <v>224</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>764</v>
@@ -9974,7 +10076,7 @@
         <v>348</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
@@ -9998,7 +10100,7 @@
         <v>226</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>768</v>
@@ -10013,7 +10115,7 @@
         <v>348</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
@@ -10037,7 +10139,7 @@
         <v>228</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>772</v>
@@ -10052,7 +10154,7 @@
         <v>348</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="J86" s="2"/>
       <c r="K86" s="2" t="s">
@@ -10067,7 +10169,7 @@
     </row>
     <row r="87" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>229</v>
@@ -10076,7 +10178,7 @@
         <v>230</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>776</v>
@@ -10091,10 +10193,10 @@
         <v>337</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>1028</v>
@@ -10108,7 +10210,7 @@
     </row>
     <row r="88" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>231</v>
@@ -10117,7 +10219,7 @@
         <v>232</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>782</v>
@@ -10132,10 +10234,10 @@
         <v>337</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>1028</v>
@@ -10149,7 +10251,7 @@
     </row>
     <row r="89" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>233</v>
@@ -10158,7 +10260,7 @@
         <v>234</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>787</v>
@@ -10173,10 +10275,10 @@
         <v>337</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>1028</v>
@@ -10190,7 +10292,7 @@
     </row>
     <row r="90" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>235</v>
@@ -10199,7 +10301,7 @@
         <v>236</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>793</v>
@@ -10214,10 +10316,10 @@
         <v>337</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>1028</v>
@@ -10231,7 +10333,7 @@
     </row>
     <row r="91" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>237</v>
@@ -10240,7 +10342,7 @@
         <v>238</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>799</v>
@@ -10255,10 +10357,10 @@
         <v>337</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="K91" s="2" t="s">
         <v>1028</v>
@@ -10272,7 +10374,7 @@
     </row>
     <row r="92" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>239</v>
@@ -10281,7 +10383,7 @@
         <v>240</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>801</v>
@@ -10296,7 +10398,7 @@
         <v>348</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="J92" s="2"/>
       <c r="K92" s="2" t="s">
@@ -10311,7 +10413,7 @@
     </row>
     <row r="93" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>241</v>
@@ -10320,7 +10422,7 @@
         <v>242</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>805</v>
@@ -10335,7 +10437,7 @@
         <v>348</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="J93" s="2"/>
       <c r="K93" s="2" t="s">
@@ -10350,7 +10452,7 @@
     </row>
     <row r="94" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>243</v>
@@ -10359,7 +10461,7 @@
         <v>244</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>809</v>
@@ -10374,10 +10476,10 @@
         <v>337</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>1028</v>
@@ -10391,7 +10493,7 @@
     </row>
     <row r="95" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>245</v>
@@ -10400,7 +10502,7 @@
         <v>246</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>811</v>
@@ -10415,7 +10517,7 @@
         <v>348</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
@@ -10430,7 +10532,7 @@
     </row>
     <row r="96" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>247</v>
@@ -10439,7 +10541,7 @@
         <v>248</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>815</v>
@@ -10454,10 +10556,10 @@
         <v>337</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="K96" s="2" t="s">
         <v>1028</v>
@@ -10471,7 +10573,7 @@
     </row>
     <row r="97" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>249</v>
@@ -10480,7 +10582,7 @@
         <v>250</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>822</v>
@@ -10495,7 +10597,7 @@
         <v>348</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="J97" s="2"/>
       <c r="K97" s="2" t="s">
@@ -10510,7 +10612,7 @@
     </row>
     <row r="98" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>251</v>
@@ -10519,7 +10621,7 @@
         <v>252</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>826</v>
@@ -10534,7 +10636,7 @@
         <v>348</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="J98" s="2"/>
       <c r="K98" s="2" t="s">
@@ -10549,7 +10651,7 @@
     </row>
     <row r="99" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>253</v>
@@ -10558,7 +10660,7 @@
         <v>254</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>830</v>
@@ -10573,7 +10675,7 @@
         <v>348</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
@@ -10588,7 +10690,7 @@
     </row>
     <row r="100" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>255</v>
@@ -10597,7 +10699,7 @@
         <v>256</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>834</v>
@@ -10612,10 +10714,10 @@
         <v>337</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>1028</v>
@@ -10629,7 +10731,7 @@
     </row>
     <row r="101" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>257</v>
@@ -10638,7 +10740,7 @@
         <v>258</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>840</v>
@@ -10653,7 +10755,7 @@
         <v>348</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2" t="s">
@@ -10668,7 +10770,7 @@
     </row>
     <row r="102" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>259</v>
@@ -10677,7 +10779,7 @@
         <v>260</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>844</v>
@@ -10692,7 +10794,7 @@
         <v>348</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="2" t="s">
@@ -10707,7 +10809,7 @@
     </row>
     <row r="103" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>261</v>
@@ -10716,7 +10818,7 @@
         <v>262</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>848</v>
@@ -10731,7 +10833,7 @@
         <v>348</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="J103" s="2"/>
       <c r="K103" s="2" t="s">
@@ -10746,7 +10848,7 @@
     </row>
     <row r="104" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>263</v>
@@ -10755,7 +10857,7 @@
         <v>264</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>852</v>
@@ -10770,7 +10872,7 @@
         <v>348</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="J104" s="2"/>
       <c r="K104" s="2" t="s">
@@ -10785,7 +10887,7 @@
     </row>
     <row r="105" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>265</v>
@@ -10794,7 +10896,7 @@
         <v>266</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>856</v>
@@ -10809,7 +10911,7 @@
         <v>348</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="J105" s="2"/>
       <c r="K105" s="2" t="s">
@@ -10824,7 +10926,7 @@
     </row>
     <row r="106" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>267</v>
@@ -10833,7 +10935,7 @@
         <v>268</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>860</v>
@@ -10848,10 +10950,10 @@
         <v>337</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>1028</v>
@@ -10865,7 +10967,7 @@
     </row>
     <row r="107" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>269</v>
@@ -10874,7 +10976,7 @@
         <v>270</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>862</v>
@@ -10889,7 +10991,7 @@
         <v>348</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="J107" s="2"/>
       <c r="K107" s="2" t="s">
@@ -10904,7 +11006,7 @@
     </row>
     <row r="108" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>271</v>
@@ -10913,7 +11015,7 @@
         <v>272</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>866</v>
@@ -10928,10 +11030,10 @@
         <v>337</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="K108" s="2" t="s">
         <v>1028</v>
@@ -10945,7 +11047,7 @@
     </row>
     <row r="109" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>273</v>
@@ -10954,7 +11056,7 @@
         <v>274</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>872</v>
@@ -10969,7 +11071,7 @@
         <v>348</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="J109" s="2"/>
       <c r="K109" s="2" t="s">
@@ -10984,7 +11086,7 @@
     </row>
     <row r="110" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>275</v>
@@ -10993,7 +11095,7 @@
         <v>276</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>876</v>
@@ -11008,7 +11110,7 @@
         <v>348</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="J110" s="2"/>
       <c r="K110" s="2" t="s">
@@ -11023,7 +11125,7 @@
     </row>
     <row r="111" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>277</v>
@@ -11032,7 +11134,7 @@
         <v>278</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>880</v>
@@ -11047,7 +11149,7 @@
         <v>348</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="J111" s="2"/>
       <c r="K111" s="2" t="s">
@@ -11062,7 +11164,7 @@
     </row>
     <row r="112" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>279</v>
@@ -11071,7 +11173,7 @@
         <v>280</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>884</v>
@@ -11086,7 +11188,7 @@
         <v>348</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="J112" s="2"/>
       <c r="K112" s="2" t="s">
@@ -11101,7 +11203,7 @@
     </row>
     <row r="113" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>281</v>
@@ -11110,7 +11212,7 @@
         <v>282</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>888</v>
@@ -11125,7 +11227,7 @@
         <v>348</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="J113" s="2"/>
       <c r="K113" s="2" t="s">
@@ -11140,7 +11242,7 @@
     </row>
     <row r="114" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>283</v>
@@ -11149,7 +11251,7 @@
         <v>284</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>892</v>
@@ -11164,7 +11266,7 @@
         <v>348</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="J114" s="2"/>
       <c r="K114" s="2" t="s">
@@ -11179,7 +11281,7 @@
     </row>
     <row r="115" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>285</v>
@@ -11188,7 +11290,7 @@
         <v>286</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>896</v>
@@ -11203,7 +11305,7 @@
         <v>348</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="J115" s="2"/>
       <c r="K115" s="2" t="s">
@@ -11218,7 +11320,7 @@
     </row>
     <row r="116" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>287</v>
@@ -11227,7 +11329,7 @@
         <v>288</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>900</v>
@@ -11242,7 +11344,7 @@
         <v>348</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="J116" s="2"/>
       <c r="K116" s="2" t="s">
@@ -11257,7 +11359,7 @@
     </row>
     <row r="117" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>289</v>
@@ -11266,7 +11368,7 @@
         <v>290</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>904</v>
@@ -11281,10 +11383,10 @@
         <v>337</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="K117" s="2" t="s">
         <v>1028</v>
@@ -11298,7 +11400,7 @@
     </row>
     <row r="118" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>291</v>
@@ -11307,7 +11409,7 @@
         <v>292</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>909</v>
@@ -11322,7 +11424,7 @@
         <v>348</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="J118" s="2"/>
       <c r="K118" s="2" t="s">
@@ -11337,7 +11439,7 @@
     </row>
     <row r="119" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>293</v>
@@ -11346,7 +11448,7 @@
         <v>294</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>913</v>
@@ -11361,7 +11463,7 @@
         <v>348</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="J119" s="2"/>
       <c r="K119" s="2" t="s">
@@ -11376,7 +11478,7 @@
     </row>
     <row r="120" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>295</v>
@@ -11385,7 +11487,7 @@
         <v>296</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>917</v>
@@ -11400,7 +11502,7 @@
         <v>348</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="J120" s="2"/>
       <c r="K120" s="2" t="s">
@@ -11415,7 +11517,7 @@
     </row>
     <row r="121" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>297</v>
@@ -11424,7 +11526,7 @@
         <v>298</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>921</v>
@@ -11439,7 +11541,7 @@
         <v>348</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="J121" s="2"/>
       <c r="K121" s="2" t="s">
@@ -11454,7 +11556,7 @@
     </row>
     <row r="122" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>299</v>
@@ -11463,7 +11565,7 @@
         <v>300</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>925</v>
@@ -11478,10 +11580,10 @@
         <v>337</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="K122" s="2" t="s">
         <v>1028</v>
@@ -11504,7 +11606,7 @@
         <v>302</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>931</v>
@@ -11519,10 +11621,10 @@
         <v>337</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="K123" s="2" t="s">
         <v>1028</v>
@@ -11545,7 +11647,7 @@
         <v>302</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>938</v>
@@ -11560,10 +11662,10 @@
         <v>337</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="K124" s="2" t="s">
         <v>1031</v>
@@ -11577,7 +11679,7 @@
     </row>
     <row r="125" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>303</v>
@@ -11586,7 +11688,7 @@
         <v>304</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>944</v>
@@ -11601,10 +11703,10 @@
         <v>337</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="K125" s="2" t="s">
         <v>1028</v>
@@ -11627,7 +11729,7 @@
         <v>306</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>950</v>
@@ -11642,10 +11744,10 @@
         <v>337</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="K126" s="2" t="s">
         <v>1028</v>
@@ -11668,7 +11770,7 @@
         <v>306</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>956</v>
@@ -11683,10 +11785,10 @@
         <v>337</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="K127" s="2" t="s">
         <v>1031</v>
@@ -11709,7 +11811,7 @@
         <v>306</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>960</v>
@@ -11724,10 +11826,10 @@
         <v>337</v>
       </c>
       <c r="I128" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="J128" s="2" t="s">
         <v>1491</v>
-      </c>
-      <c r="J128" s="2" t="s">
-        <v>1489</v>
       </c>
       <c r="K128" s="2" t="s">
         <v>1028</v>
@@ -11750,7 +11852,7 @@
         <v>308</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>965</v>
@@ -11765,10 +11867,10 @@
         <v>337</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="K129" s="2" t="s">
         <v>1028</v>
@@ -11791,7 +11893,7 @@
         <v>308</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>972</v>
@@ -11806,10 +11908,10 @@
         <v>337</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>1028</v>
@@ -11832,7 +11934,7 @@
         <v>308</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>978</v>
@@ -11847,10 +11949,10 @@
         <v>337</v>
       </c>
       <c r="I131" s="2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="J131" s="2" t="s">
         <v>1496</v>
-      </c>
-      <c r="J131" s="2" t="s">
-        <v>1494</v>
       </c>
       <c r="K131" s="2" t="s">
         <v>1028</v>
@@ -11873,7 +11975,7 @@
         <v>308</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>983</v>
@@ -11888,10 +11990,10 @@
         <v>337</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="K132" s="2" t="s">
         <v>1028</v>
@@ -11914,7 +12016,7 @@
         <v>310</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>988</v>
@@ -11929,10 +12031,10 @@
         <v>337</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>1028</v>
@@ -11955,7 +12057,7 @@
         <v>310</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>994</v>
@@ -11970,10 +12072,10 @@
         <v>337</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="K134" s="2" t="s">
         <v>1028</v>
@@ -11996,7 +12098,7 @@
         <v>310</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>1000</v>
@@ -12011,10 +12113,10 @@
         <v>337</v>
       </c>
       <c r="I135" s="2" t="s">
+        <v>1504</v>
+      </c>
+      <c r="J135" s="2" t="s">
         <v>1502</v>
-      </c>
-      <c r="J135" s="2" t="s">
-        <v>1500</v>
       </c>
       <c r="K135" s="2" t="s">
         <v>1028</v>
@@ -12037,7 +12139,7 @@
         <v>310</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>1006</v>
@@ -12052,10 +12154,10 @@
         <v>337</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="K136" s="2" t="s">
         <v>1031</v>
@@ -12078,7 +12180,7 @@
         <v>312</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>1012</v>
@@ -12093,10 +12195,10 @@
         <v>337</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="K137" s="2" t="s">
         <v>1028</v>
@@ -12119,7 +12221,7 @@
         <v>312</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>1018</v>
@@ -12134,10 +12236,10 @@
         <v>337</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="K138" s="2" t="s">
         <v>1028</v>
@@ -12169,36 +12271,36 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
     </row>
   </sheetData>
@@ -12221,7 +12323,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>314</v>
@@ -12230,180 +12332,180 @@
         <v>1071</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
     </row>
   </sheetData>
@@ -12426,186 +12528,186 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
     </row>
   </sheetData>
@@ -21603,7 +21705,7 @@
         <v>1028</v>
       </c>
       <c r="E2" s="2">
-        <v>539</v>
+        <v>505</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -21721,7 +21823,7 @@
         <v>1028</v>
       </c>
       <c r="E8" s="2">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -21739,7 +21841,7 @@
         <v>1028</v>
       </c>
       <c r="E9" s="2">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -21757,7 +21859,7 @@
         <v>1028</v>
       </c>
       <c r="E10" s="2">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -21775,7 +21877,7 @@
         <v>1028</v>
       </c>
       <c r="E11" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -21793,7 +21895,7 @@
         <v>1028</v>
       </c>
       <c r="E12" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -21811,7 +21913,7 @@
         <v>1028</v>
       </c>
       <c r="E13" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -21889,7 +21991,7 @@
         <v>1028</v>
       </c>
       <c r="E17" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -21907,7 +22009,7 @@
         <v>1028</v>
       </c>
       <c r="E18" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -21985,7 +22087,7 @@
         <v>1028</v>
       </c>
       <c r="E22" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F22" s="2"/>
     </row>
@@ -22041,7 +22143,7 @@
         <v>1028</v>
       </c>
       <c r="E25" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -22095,7 +22197,7 @@
         <v>1028</v>
       </c>
       <c r="E28" s="2">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -22113,7 +22215,7 @@
         <v>1028</v>
       </c>
       <c r="E29" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -22131,7 +22233,7 @@
         <v>1028</v>
       </c>
       <c r="E30" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -22149,7 +22251,7 @@
         <v>1028</v>
       </c>
       <c r="E31" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -22167,7 +22269,7 @@
         <v>1028</v>
       </c>
       <c r="E32" s="2">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F32" s="2"/>
     </row>
@@ -22205,7 +22307,7 @@
         <v>1028</v>
       </c>
       <c r="E34" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -22223,7 +22325,7 @@
         <v>1028</v>
       </c>
       <c r="E35" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F35" s="2"/>
     </row>
@@ -22281,7 +22383,7 @@
         <v>1028</v>
       </c>
       <c r="E38" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F38" s="2"/>
     </row>
@@ -22319,7 +22421,7 @@
         <v>1028</v>
       </c>
       <c r="E40" s="2">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -22337,7 +22439,7 @@
         <v>1028</v>
       </c>
       <c r="E41" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F41" s="2"/>
     </row>
@@ -22435,7 +22537,7 @@
         <v>1028</v>
       </c>
       <c r="E46" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -22453,7 +22555,7 @@
         <v>1028</v>
       </c>
       <c r="E47" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -22471,7 +22573,7 @@
         <v>1028</v>
       </c>
       <c r="E48" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F48" s="2"/>
     </row>
@@ -22509,7 +22611,7 @@
         <v>1028</v>
       </c>
       <c r="E50" s="2">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -22527,7 +22629,7 @@
         <v>1028</v>
       </c>
       <c r="E51" s="2">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -22545,7 +22647,7 @@
         <v>1028</v>
       </c>
       <c r="E52" s="2">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F52" s="2"/>
     </row>
@@ -22663,7 +22765,7 @@
         <v>1028</v>
       </c>
       <c r="E58" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -22681,7 +22783,7 @@
         <v>1028</v>
       </c>
       <c r="E59" s="2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F59" s="2"/>
     </row>
@@ -22719,7 +22821,7 @@
         <v>1028</v>
       </c>
       <c r="E61" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F61" s="2"/>
     </row>
@@ -22817,7 +22919,7 @@
         <v>1028</v>
       </c>
       <c r="E66" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -22835,7 +22937,7 @@
         <v>1028</v>
       </c>
       <c r="E67" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -22853,7 +22955,7 @@
         <v>1028</v>
       </c>
       <c r="E68" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F68" s="2"/>
     </row>
@@ -22911,7 +23013,7 @@
         <v>1028</v>
       </c>
       <c r="E71" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -22947,7 +23049,7 @@
         <v>1028</v>
       </c>
       <c r="E73" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F73" s="2"/>
     </row>
@@ -23003,7 +23105,7 @@
         <v>1028</v>
       </c>
       <c r="E76" s="2">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -23021,7 +23123,7 @@
         <v>1028</v>
       </c>
       <c r="E77" s="2">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -23097,7 +23199,7 @@
         <v>1028</v>
       </c>
       <c r="E81" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -23115,7 +23217,7 @@
         <v>1028</v>
       </c>
       <c r="E82" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -23133,7 +23235,7 @@
         <v>1028</v>
       </c>
       <c r="E83" s="2">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F83" s="2"/>
     </row>
@@ -23211,7 +23313,7 @@
         <v>1028</v>
       </c>
       <c r="E87" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -23229,7 +23331,7 @@
         <v>1028</v>
       </c>
       <c r="E88" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -23247,7 +23349,7 @@
         <v>1028</v>
       </c>
       <c r="E89" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -23265,7 +23367,7 @@
         <v>1028</v>
       </c>
       <c r="E90" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -23283,7 +23385,7 @@
         <v>1028</v>
       </c>
       <c r="E91" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F91" s="2"/>
     </row>
@@ -23341,7 +23443,7 @@
         <v>1028</v>
       </c>
       <c r="E94" s="2">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -23379,7 +23481,7 @@
         <v>1028</v>
       </c>
       <c r="E96" s="2">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="F96" s="2"/>
     </row>
@@ -23457,7 +23559,7 @@
         <v>1028</v>
       </c>
       <c r="E100" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F100" s="2"/>
     </row>
@@ -23575,7 +23677,7 @@
         <v>1028</v>
       </c>
       <c r="E106" s="2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -23613,7 +23715,7 @@
         <v>1028</v>
       </c>
       <c r="E108" s="2">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F108" s="2"/>
     </row>
@@ -23791,7 +23893,7 @@
         <v>1028</v>
       </c>
       <c r="E117" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -23889,7 +23991,7 @@
         <v>1028</v>
       </c>
       <c r="E122" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -23907,7 +24009,7 @@
         <v>1028</v>
       </c>
       <c r="E123" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -23925,7 +24027,7 @@
         <v>1031</v>
       </c>
       <c r="E124" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -23979,7 +24081,7 @@
         <v>1031</v>
       </c>
       <c r="E127" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -23997,7 +24099,7 @@
         <v>1028</v>
       </c>
       <c r="E128" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -24015,7 +24117,7 @@
         <v>1028</v>
       </c>
       <c r="E129" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -24033,7 +24135,7 @@
         <v>1028</v>
       </c>
       <c r="E130" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -24051,7 +24153,7 @@
         <v>1028</v>
       </c>
       <c r="E131" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -24069,7 +24171,7 @@
         <v>1028</v>
       </c>
       <c r="E132" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -24087,7 +24189,7 @@
         <v>1028</v>
       </c>
       <c r="E133" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F133" s="2"/>
     </row>
@@ -24105,7 +24207,7 @@
         <v>1028</v>
       </c>
       <c r="E134" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F134" s="2"/>
     </row>
@@ -24123,7 +24225,7 @@
         <v>1028</v>
       </c>
       <c r="E135" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F135" s="2"/>
     </row>
@@ -24141,7 +24243,7 @@
         <v>1031</v>
       </c>
       <c r="E136" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F136" s="2"/>
     </row>
@@ -24159,7 +24261,7 @@
         <v>1028</v>
       </c>
       <c r="E137" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F137" s="2"/>
     </row>
@@ -24177,7 +24279,7 @@
         <v>1028</v>
       </c>
       <c r="E138" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F138" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/09-report/CYC-2-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/09-report/CYC-2-cycle-report.xlsx
@@ -170,7 +170,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-02T20:25:59.721Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-02T20:28:41.785Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -4633,7 +4633,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T20:26:00.496Z</t>
+    <t>2026-10-02T20:28:42.687Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -21705,7 +21705,7 @@
         <v>1028</v>
       </c>
       <c r="E2" s="2">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -21823,7 +21823,7 @@
         <v>1028</v>
       </c>
       <c r="E8" s="2">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -21841,7 +21841,7 @@
         <v>1028</v>
       </c>
       <c r="E9" s="2">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -21859,7 +21859,7 @@
         <v>1028</v>
       </c>
       <c r="E10" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -21877,7 +21877,7 @@
         <v>1028</v>
       </c>
       <c r="E11" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -21895,7 +21895,7 @@
         <v>1028</v>
       </c>
       <c r="E12" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -21913,7 +21913,7 @@
         <v>1028</v>
       </c>
       <c r="E13" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -21991,7 +21991,7 @@
         <v>1028</v>
       </c>
       <c r="E17" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -22087,7 +22087,7 @@
         <v>1028</v>
       </c>
       <c r="E22" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F22" s="2"/>
     </row>
@@ -22125,7 +22125,7 @@
         <v>1028</v>
       </c>
       <c r="E24" s="2">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -22143,7 +22143,7 @@
         <v>1028</v>
       </c>
       <c r="E25" s="2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -22161,7 +22161,7 @@
         <v>1028</v>
       </c>
       <c r="E26" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -22179,7 +22179,7 @@
         <v>1028</v>
       </c>
       <c r="E27" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -22197,7 +22197,7 @@
         <v>1028</v>
       </c>
       <c r="E28" s="2">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -22215,7 +22215,7 @@
         <v>1028</v>
       </c>
       <c r="E29" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -22233,7 +22233,7 @@
         <v>1028</v>
       </c>
       <c r="E30" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -22269,7 +22269,7 @@
         <v>1028</v>
       </c>
       <c r="E32" s="2">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F32" s="2"/>
     </row>
@@ -22307,7 +22307,7 @@
         <v>1028</v>
       </c>
       <c r="E34" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -22383,7 +22383,7 @@
         <v>1028</v>
       </c>
       <c r="E38" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F38" s="2"/>
     </row>
@@ -22421,7 +22421,7 @@
         <v>1028</v>
       </c>
       <c r="E40" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -22439,7 +22439,7 @@
         <v>1028</v>
       </c>
       <c r="E41" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F41" s="2"/>
     </row>
@@ -22537,7 +22537,7 @@
         <v>1028</v>
       </c>
       <c r="E46" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -22555,7 +22555,7 @@
         <v>1028</v>
       </c>
       <c r="E47" s="2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -22573,7 +22573,7 @@
         <v>1028</v>
       </c>
       <c r="E48" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F48" s="2"/>
     </row>
@@ -22611,7 +22611,7 @@
         <v>1028</v>
       </c>
       <c r="E50" s="2">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -22629,7 +22629,7 @@
         <v>1028</v>
       </c>
       <c r="E51" s="2">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -22647,7 +22647,7 @@
         <v>1028</v>
       </c>
       <c r="E52" s="2">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F52" s="2"/>
     </row>
@@ -22765,7 +22765,7 @@
         <v>1028</v>
       </c>
       <c r="E58" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -22783,7 +22783,7 @@
         <v>1028</v>
       </c>
       <c r="E59" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F59" s="2"/>
     </row>
@@ -22821,7 +22821,7 @@
         <v>1028</v>
       </c>
       <c r="E61" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F61" s="2"/>
     </row>
@@ -22937,7 +22937,7 @@
         <v>1028</v>
       </c>
       <c r="E67" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -22955,7 +22955,7 @@
         <v>1028</v>
       </c>
       <c r="E68" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F68" s="2"/>
     </row>
@@ -23013,7 +23013,7 @@
         <v>1028</v>
       </c>
       <c r="E71" s="2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -23105,7 +23105,7 @@
         <v>1028</v>
       </c>
       <c r="E76" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -23123,7 +23123,7 @@
         <v>1028</v>
       </c>
       <c r="E77" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -23199,7 +23199,7 @@
         <v>1028</v>
       </c>
       <c r="E81" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -23217,7 +23217,7 @@
         <v>1028</v>
       </c>
       <c r="E82" s="2">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -23235,7 +23235,7 @@
         <v>1028</v>
       </c>
       <c r="E83" s="2">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F83" s="2"/>
     </row>
@@ -23313,7 +23313,7 @@
         <v>1028</v>
       </c>
       <c r="E87" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -23331,7 +23331,7 @@
         <v>1028</v>
       </c>
       <c r="E88" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -23349,7 +23349,7 @@
         <v>1028</v>
       </c>
       <c r="E89" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -23367,7 +23367,7 @@
         <v>1028</v>
       </c>
       <c r="E90" s="2">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -23385,7 +23385,7 @@
         <v>1028</v>
       </c>
       <c r="E91" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F91" s="2"/>
     </row>
@@ -23443,7 +23443,7 @@
         <v>1028</v>
       </c>
       <c r="E94" s="2">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -23481,7 +23481,7 @@
         <v>1028</v>
       </c>
       <c r="E96" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F96" s="2"/>
     </row>
@@ -23559,7 +23559,7 @@
         <v>1028</v>
       </c>
       <c r="E100" s="2">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="F100" s="2"/>
     </row>
@@ -23677,7 +23677,7 @@
         <v>1028</v>
       </c>
       <c r="E106" s="2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -23715,7 +23715,7 @@
         <v>1028</v>
       </c>
       <c r="E108" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F108" s="2"/>
     </row>
@@ -23893,7 +23893,7 @@
         <v>1028</v>
       </c>
       <c r="E117" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -23991,7 +23991,7 @@
         <v>1028</v>
       </c>
       <c r="E122" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -24027,7 +24027,7 @@
         <v>1031</v>
       </c>
       <c r="E124" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -24081,7 +24081,7 @@
         <v>1031</v>
       </c>
       <c r="E127" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -24099,7 +24099,7 @@
         <v>1028</v>
       </c>
       <c r="E128" s="2">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -24135,7 +24135,7 @@
         <v>1028</v>
       </c>
       <c r="E130" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -24153,7 +24153,7 @@
         <v>1028</v>
       </c>
       <c r="E131" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -24225,7 +24225,7 @@
         <v>1028</v>
       </c>
       <c r="E135" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F135" s="2"/>
     </row>
@@ -24261,7 +24261,7 @@
         <v>1028</v>
       </c>
       <c r="E137" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F137" s="2"/>
     </row>
@@ -24279,7 +24279,7 @@
         <v>1028</v>
       </c>
       <c r="E138" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F138" s="2"/>
     </row>
